--- a/Results_isofys/SFtraits_complete.xlsx
+++ b/Results_isofys/SFtraits_complete.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\NUMEX_preliminar\Results_isofys\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\SLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15780" windowHeight="5670"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="51">
   <si>
     <t>Plot_x</t>
   </si>
@@ -99,6 +99,9 @@
     <t>Leaf area (cm²)</t>
   </si>
   <si>
+    <t>Plot</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
   </si>
   <si>
     <t>19</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -614,20 +620,22 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>69</v>
@@ -684,7 +692,7 @@
         <v>0.93375439562890372</v>
       </c>
       <c r="X2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y2">
         <v>69</v>
@@ -698,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>88</v>
@@ -761,7 +769,7 @@
         <v>0.64353137799262627</v>
       </c>
       <c r="X3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y3">
         <v>88</v>
@@ -775,13 +783,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>4966</v>
@@ -841,7 +849,7 @@
         <v>0.67216469219590569</v>
       </c>
       <c r="X4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y4">
         <v>90</v>
@@ -855,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>92</v>
@@ -918,7 +926,7 @@
         <v>0.54945171314582775</v>
       </c>
       <c r="X5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y5">
         <v>92</v>
@@ -932,13 +940,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -995,7 +1003,7 @@
         <v>0.5953654546153796</v>
       </c>
       <c r="X6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y6">
         <v>96</v>
@@ -1009,13 +1017,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>101</v>
@@ -1072,7 +1080,7 @@
         <v>0.52146683887209699</v>
       </c>
       <c r="X7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y7">
         <v>101</v>
@@ -1086,13 +1094,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>9091</v>
@@ -1149,7 +1157,7 @@
         <v>0.30996191628373221</v>
       </c>
       <c r="X8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y8">
         <v>9091</v>
@@ -1163,13 +1171,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>9096</v>
@@ -1226,7 +1234,7 @@
         <v>0.50296884701541678</v>
       </c>
       <c r="X9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y9">
         <v>9096</v>
@@ -1240,13 +1248,13 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>254</v>
@@ -1303,7 +1311,7 @@
         <v>0.67448670723073889</v>
       </c>
       <c r="X10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y10">
         <v>254</v>
@@ -1317,13 +1325,13 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>267</v>
@@ -1380,7 +1388,7 @@
         <v>0.66634530256369617</v>
       </c>
       <c r="X11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y11">
         <v>267</v>
@@ -1394,13 +1402,13 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>141</v>
@@ -1457,7 +1465,7 @@
         <v>0.67888952384523749</v>
       </c>
       <c r="X12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y12">
         <v>141</v>
@@ -1471,13 +1479,13 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>143</v>
@@ -1534,7 +1542,7 @@
         <v>1.3602653623084251</v>
       </c>
       <c r="X13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y13">
         <v>143</v>
@@ -1548,13 +1556,13 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>155</v>
@@ -1611,7 +1619,7 @@
         <v>0.8671868366505725</v>
       </c>
       <c r="X14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y14">
         <v>155</v>
@@ -1625,13 +1633,13 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15">
         <v>172</v>
@@ -1688,7 +1696,7 @@
         <v>0.85954961186370971</v>
       </c>
       <c r="X15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y15">
         <v>172</v>
@@ -1702,13 +1710,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16">
         <v>188</v>
@@ -1765,7 +1773,7 @@
         <v>0.58545855970023564</v>
       </c>
       <c r="X16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y16">
         <v>188</v>
@@ -1779,13 +1787,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <v>191</v>
@@ -1842,7 +1850,7 @@
         <v>0.67055111744776807</v>
       </c>
       <c r="X17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y17">
         <v>191</v>
@@ -1856,13 +1864,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>200</v>
@@ -1919,7 +1927,7 @@
         <v>0.71175443978373909</v>
       </c>
       <c r="X18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y18">
         <v>200</v>
@@ -1933,13 +1941,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>205</v>
@@ -1996,7 +2004,7 @@
         <v>0.69790416786521037</v>
       </c>
       <c r="X19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y19">
         <v>205</v>
@@ -2010,13 +2018,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20">
         <v>209</v>
@@ -2073,7 +2081,7 @@
         <v>1.4227986302889579</v>
       </c>
       <c r="X20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y20">
         <v>209</v>
@@ -2087,13 +2095,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21">
         <v>213</v>
@@ -2150,7 +2158,7 @@
         <v>0.63824183053382444</v>
       </c>
       <c r="X21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y21">
         <v>213</v>
@@ -2164,13 +2172,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22">
         <v>219</v>
@@ -2227,7 +2235,7 @@
         <v>0.70762505809660969</v>
       </c>
       <c r="X22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y22">
         <v>219</v>
@@ -2241,13 +2249,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23">
         <v>286</v>
@@ -2304,7 +2312,7 @@
         <v>0.65198182136378591</v>
       </c>
       <c r="X23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y23">
         <v>286</v>
@@ -2318,13 +2326,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24">
         <v>290</v>
@@ -2381,7 +2389,7 @@
         <v>1.152817493965886</v>
       </c>
       <c r="X24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y24">
         <v>290</v>
@@ -2395,13 +2403,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F25">
         <v>310</v>
@@ -2458,7 +2466,7 @@
         <v>0.82568518152160986</v>
       </c>
       <c r="X25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y25">
         <v>310</v>
@@ -2472,13 +2480,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F26">
         <v>6021</v>
@@ -2535,7 +2543,7 @@
         <v>0.65361373069631201</v>
       </c>
       <c r="X26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y26">
         <v>6021</v>
@@ -2549,13 +2557,13 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>333</v>
@@ -2612,7 +2620,7 @@
         <v>0.67284165998378676</v>
       </c>
       <c r="X27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y27">
         <v>333</v>
@@ -2626,13 +2634,13 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28">
         <v>335</v>
@@ -2689,7 +2697,7 @@
         <v>0.60745506559882334</v>
       </c>
       <c r="X28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y28">
         <v>335</v>
@@ -2703,13 +2711,13 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29">
         <v>341</v>
@@ -2766,7 +2774,7 @@
         <v>0.64538435640185099</v>
       </c>
       <c r="X29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y29">
         <v>341</v>
@@ -2780,13 +2788,13 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30">
         <v>356</v>
@@ -2843,7 +2851,7 @@
         <v>0.62731443320284119</v>
       </c>
       <c r="X30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y30">
         <v>356</v>
@@ -2857,13 +2865,13 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>6994</v>
@@ -2920,7 +2928,7 @@
         <v>0.73289884442324349</v>
       </c>
       <c r="X31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y31">
         <v>6994</v>
@@ -2934,13 +2942,13 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32">
         <v>7994</v>
@@ -2997,7 +3005,7 @@
         <v>0.60720166686426202</v>
       </c>
       <c r="X32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y32">
         <v>7994</v>
@@ -3011,13 +3019,13 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
         <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
       </c>
       <c r="F33">
         <v>378</v>
@@ -3074,7 +3082,7 @@
         <v>0.54955023184554519</v>
       </c>
       <c r="X33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y33">
         <v>378</v>
@@ -3088,13 +3096,13 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>389</v>
@@ -3151,7 +3159,7 @@
         <v>0.65267718541780073</v>
       </c>
       <c r="X34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y34">
         <v>389</v>
@@ -3165,13 +3173,13 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F35">
         <v>410</v>
@@ -3228,7 +3236,7 @@
         <v>0.9163775544555931</v>
       </c>
       <c r="X35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y35">
         <v>410</v>
@@ -3242,13 +3250,13 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
         <v>32</v>
-      </c>
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
       </c>
       <c r="F36">
         <v>9080</v>
@@ -3305,7 +3313,7 @@
         <v>0.39055729029571518</v>
       </c>
       <c r="X36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y36">
         <v>9080</v>
@@ -3319,13 +3327,13 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F37">
         <v>569</v>
@@ -3382,7 +3390,7 @@
         <v>0.6895798104979235</v>
       </c>
       <c r="X37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y37">
         <v>569</v>
@@ -3396,13 +3404,13 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F38">
         <v>575</v>
@@ -3459,7 +3467,7 @@
         <v>0.57025958917460684</v>
       </c>
       <c r="X38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y38">
         <v>575</v>
@@ -3473,13 +3481,13 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
         <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
       </c>
       <c r="F39">
         <v>580</v>
@@ -3536,7 +3544,7 @@
         <v>1.392603334482716</v>
       </c>
       <c r="X39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y39">
         <v>580</v>
@@ -3550,13 +3558,13 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F40">
         <v>587</v>
@@ -3613,7 +3621,7 @@
         <v>0.65272487799156209</v>
       </c>
       <c r="X40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y40">
         <v>587</v>
@@ -3627,13 +3635,13 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F41">
         <v>596</v>
@@ -3690,7 +3698,7 @@
         <v>0.57119399416423045</v>
       </c>
       <c r="X41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y41">
         <v>596</v>
@@ -3704,13 +3712,13 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" t="s">
         <v>32</v>
-      </c>
-      <c r="C42" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" t="s">
-        <v>31</v>
       </c>
       <c r="F42">
         <v>915</v>
@@ -3767,7 +3775,7 @@
         <v>0.65619644928845844</v>
       </c>
       <c r="X42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y42">
         <v>915</v>
@@ -3781,13 +3789,13 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F43">
         <v>708</v>
@@ -3844,7 +3852,7 @@
         <v>1.0749599826320391</v>
       </c>
       <c r="X43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y43">
         <v>708</v>
@@ -3858,13 +3866,13 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F44">
         <v>721</v>
@@ -3921,7 +3929,7 @@
         <v>0.86234695562764752</v>
       </c>
       <c r="X44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y44">
         <v>721</v>
@@ -3935,13 +3943,13 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F45">
         <v>729</v>
@@ -3998,7 +4006,7 @@
         <v>0.82236954012352836</v>
       </c>
       <c r="X45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y45">
         <v>729</v>
@@ -4012,13 +4020,13 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F46">
         <v>627</v>
@@ -4075,7 +4083,7 @@
         <v>0.58739035651902571</v>
       </c>
       <c r="X46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y46">
         <v>627</v>
@@ -4089,13 +4097,13 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F47">
         <v>631</v>
@@ -4152,7 +4160,7 @@
         <v>0.51926604097941564</v>
       </c>
       <c r="X47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y47">
         <v>631</v>
@@ -4166,13 +4174,13 @@
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F48">
         <v>642</v>
@@ -4229,7 +4237,7 @@
         <v>0.75479895908546057</v>
       </c>
       <c r="X48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y48">
         <v>642</v>
@@ -4243,13 +4251,13 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F49">
         <v>9742</v>
@@ -4306,7 +4314,7 @@
         <v>0.74099114632419627</v>
       </c>
       <c r="X49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y49">
         <v>9742</v>
@@ -4320,13 +4328,13 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50">
         <v>659</v>
@@ -4383,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="X50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y50">
         <v>659</v>
@@ -4397,13 +4405,13 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F51">
         <v>666</v>
@@ -4460,7 +4468,7 @@
         <v>0.75540141003846228</v>
       </c>
       <c r="X51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y51">
         <v>666</v>
@@ -4474,13 +4482,13 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F52">
         <v>685</v>
@@ -4537,7 +4545,7 @@
         <v>0.77794552241096226</v>
       </c>
       <c r="X52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y52">
         <v>685</v>
@@ -4551,13 +4559,13 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F53">
         <v>693</v>
@@ -4614,7 +4622,7 @@
         <v>0.73874634149960039</v>
       </c>
       <c r="X53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y53">
         <v>693</v>
@@ -4628,13 +4636,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" t="s">
         <v>32</v>
-      </c>
-      <c r="C54" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
       </c>
       <c r="F54">
         <v>740</v>
@@ -4691,7 +4699,7 @@
         <v>0.51968405938420781</v>
       </c>
       <c r="X54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y54">
         <v>740</v>
@@ -4705,13 +4713,13 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="s">
         <v>32</v>
-      </c>
-      <c r="C55" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
       </c>
       <c r="F55">
         <v>746</v>
@@ -4768,7 +4776,7 @@
         <v>0.50188962336462528</v>
       </c>
       <c r="X55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y55">
         <v>746</v>
@@ -4782,13 +4790,13 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F56">
         <v>755</v>
@@ -4845,7 +4853,7 @@
         <v>0.66859423229833526</v>
       </c>
       <c r="X56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y56">
         <v>755</v>
@@ -4859,13 +4867,13 @@
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>763</v>
@@ -4922,7 +4930,7 @@
         <v>0.5161964358633585</v>
       </c>
       <c r="X57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y57">
         <v>763</v>
@@ -4936,13 +4944,13 @@
         <v>16</v>
       </c>
       <c r="B58" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58" t="s">
         <v>32</v>
-      </c>
-      <c r="C58" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" t="s">
-        <v>31</v>
       </c>
       <c r="F58">
         <v>764</v>
@@ -4999,7 +5007,7 @@
         <v>0.63599797304952554</v>
       </c>
       <c r="X58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y58">
         <v>764</v>
@@ -5013,13 +5021,13 @@
         <v>16</v>
       </c>
       <c r="B59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" t="s">
         <v>32</v>
-      </c>
-      <c r="C59" t="s">
-        <v>30</v>
-      </c>
-      <c r="D59" t="s">
-        <v>31</v>
       </c>
       <c r="F59">
         <v>768</v>
@@ -5076,7 +5084,7 @@
         <v>0.72542985723080833</v>
       </c>
       <c r="X59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y59">
         <v>768</v>
@@ -5090,13 +5098,13 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F60">
         <v>881</v>
@@ -5153,7 +5161,7 @@
         <v>0.81765344957248842</v>
       </c>
       <c r="X60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y60">
         <v>881</v>
@@ -5167,13 +5175,13 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F61">
         <v>902</v>
@@ -5230,7 +5238,7 @@
         <v>2.2789143560634089</v>
       </c>
       <c r="X61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y61">
         <v>902</v>
@@ -5244,153 +5252,153 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F62">
-        <v>8954</v>
+        <v>4933</v>
       </c>
       <c r="G62" s="2">
-        <v>45290</v>
+        <v>45294</v>
       </c>
       <c r="H62">
         <v>20</v>
       </c>
       <c r="I62">
-        <v>37.94</v>
+        <v>17.09</v>
       </c>
       <c r="J62">
-        <v>17.75</v>
+        <v>8.77</v>
       </c>
       <c r="K62">
-        <v>467.84396415392729</v>
+        <v>513.16559391456997</v>
       </c>
       <c r="L62">
-        <v>0.40433333333333332</v>
+        <v>0.46266666666666662</v>
       </c>
       <c r="M62">
-        <v>1.2981738191528931</v>
+        <v>1.5241738383433849</v>
       </c>
       <c r="N62">
-        <v>503.96010999999999</v>
+        <v>498.50623999999999</v>
       </c>
       <c r="O62">
-        <v>10.54899</v>
+        <v>10.546279999999999</v>
       </c>
       <c r="P62">
-        <v>0.435002842237245</v>
+        <v>0.42316206951753421</v>
       </c>
       <c r="Q62">
-        <v>2.1517719853094721E-2</v>
+        <v>7.7413465076342294E-2</v>
       </c>
       <c r="R62">
-        <v>1.735047838399798</v>
+        <v>0.8864310941421033</v>
       </c>
       <c r="S62">
-        <v>5.5468875293054373E-2</v>
+        <v>4.7952576796205883E-2</v>
       </c>
       <c r="T62">
-        <v>3.2479710009578491</v>
+        <v>3.457335577835881</v>
       </c>
       <c r="U62">
-        <v>1.07579931228647</v>
+        <v>0.66432459277088485</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.47255541116350408</v>
+        <v>0.46010346073571751</v>
       </c>
       <c r="X62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y62">
-        <v>8954</v>
+        <v>4933</v>
       </c>
       <c r="Z62">
-        <v>770.35500000000002</v>
+        <v>282.59800000000001</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>816</v>
+        <v>8954</v>
       </c>
       <c r="G63" s="2">
-        <v>45296</v>
+        <v>45290</v>
       </c>
       <c r="H63">
         <v>20</v>
       </c>
       <c r="I63">
-        <v>23.72</v>
+        <v>37.94</v>
       </c>
       <c r="J63">
-        <v>12.09</v>
+        <v>17.75</v>
       </c>
       <c r="K63">
-        <v>509.69645868465432</v>
+        <v>467.84396415392729</v>
       </c>
       <c r="L63">
-        <v>0.48699999999999988</v>
+        <v>0.40433333333333332</v>
       </c>
       <c r="M63">
-        <v>1.4390259437892201</v>
+        <v>1.2981738191528931</v>
       </c>
       <c r="N63">
-        <v>499.82368000000002</v>
+        <v>503.96010999999999</v>
       </c>
       <c r="O63">
-        <v>10.852690000000001</v>
+        <v>10.54899</v>
       </c>
       <c r="P63">
-        <v>0.54538091053108839</v>
+        <v>0.435002842237245</v>
       </c>
       <c r="Q63">
-        <v>6.7755572560547039E-2</v>
+        <v>2.1517719853094721E-2</v>
       </c>
       <c r="R63">
-        <v>0.8484582214873132</v>
+        <v>1.735047838399798</v>
       </c>
       <c r="S63">
-        <v>5.4013432419926038E-2</v>
+        <v>5.5468875293054373E-2</v>
       </c>
       <c r="T63">
-        <v>2.7126253073012592</v>
+        <v>3.2479710009578491</v>
       </c>
       <c r="U63">
-        <v>1.566853062813601</v>
+        <v>1.07579931228647</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>4.3087054495614536</v>
+        <v>0.47255541116350408</v>
       </c>
       <c r="X63" t="s">
         <v>47</v>
       </c>
       <c r="Y63">
-        <v>816</v>
+        <v>8954</v>
       </c>
       <c r="Z63">
-        <v>403.86</v>
+        <v>770.35500000000002</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
@@ -5398,170 +5406,170 @@
         <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F64">
-        <v>7578</v>
+        <v>816</v>
       </c>
       <c r="G64" s="2">
-        <v>45294</v>
+        <v>45296</v>
       </c>
       <c r="H64">
         <v>20</v>
       </c>
       <c r="I64">
-        <v>20.27</v>
+        <v>23.72</v>
       </c>
       <c r="J64">
-        <v>9.94</v>
+        <v>12.09</v>
       </c>
       <c r="K64">
-        <v>490.37987173162298</v>
+        <v>509.69645868465432</v>
       </c>
       <c r="L64">
-        <v>0.45800000000000002</v>
+        <v>0.48699999999999988</v>
       </c>
       <c r="M64">
-        <v>1.483589327854951</v>
+        <v>1.4390259437892201</v>
       </c>
       <c r="N64">
-        <v>497.41798</v>
+        <v>499.82368000000002</v>
       </c>
       <c r="O64">
-        <v>12.31141</v>
+        <v>10.852690000000001</v>
       </c>
       <c r="P64">
-        <v>0.75355002019089568</v>
+        <v>0.54538091053108839</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>6.7755572560547039E-2</v>
       </c>
       <c r="R64">
-        <v>0.91089225182615319</v>
+        <v>0.8484582214873132</v>
       </c>
       <c r="S64">
-        <v>7.075198559816534E-2</v>
+        <v>5.4013432419926038E-2</v>
       </c>
       <c r="T64">
-        <v>3.492996381930384</v>
+        <v>2.7126253073012592</v>
       </c>
       <c r="U64">
-        <v>0.68415421651038144</v>
+        <v>1.566853062813601</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.27510476713466719</v>
+        <v>4.3087054495614536</v>
       </c>
       <c r="X64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y64">
+        <v>816</v>
+      </c>
+      <c r="Z64">
+        <v>403.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65">
         <v>7578</v>
       </c>
-      <c r="Z64">
-        <v>360.99099999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>19</v>
-      </c>
-      <c r="B65" t="s">
-        <v>34</v>
-      </c>
-      <c r="C65" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65">
-        <v>795</v>
-      </c>
       <c r="G65" s="2">
-        <v>45297</v>
+        <v>45294</v>
       </c>
       <c r="H65">
         <v>20</v>
       </c>
       <c r="I65">
-        <v>21.26</v>
+        <v>20.27</v>
       </c>
       <c r="J65">
-        <v>10.67</v>
+        <v>9.94</v>
       </c>
       <c r="K65">
-        <v>501.88146754468482</v>
+        <v>490.37987173162298</v>
       </c>
       <c r="L65">
-        <v>0.47449999999999992</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="M65">
-        <v>1.37324190064457</v>
+        <v>1.483589327854951</v>
       </c>
       <c r="N65">
-        <v>501.64886000000013</v>
+        <v>497.41798</v>
       </c>
       <c r="O65">
-        <v>11.83794</v>
+        <v>12.31141</v>
       </c>
       <c r="P65">
-        <v>0.39494399378970019</v>
+        <v>0.75355002019089568</v>
       </c>
       <c r="Q65">
         <v>0</v>
       </c>
       <c r="R65">
-        <v>0.59773040009628187</v>
+        <v>0.91089225182615319</v>
       </c>
       <c r="S65">
-        <v>4.0156782830422129E-2</v>
+        <v>7.075198559816534E-2</v>
       </c>
       <c r="T65">
-        <v>3.8796790720398611</v>
+        <v>3.492996381930384</v>
       </c>
       <c r="U65">
-        <v>1.080636963642936</v>
+        <v>0.68415421651038144</v>
       </c>
       <c r="V65">
-        <v>7.5892213728818658E-2</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>0.88961263793631462</v>
+        <v>0.27510476713466719</v>
       </c>
       <c r="X65" t="s">
         <v>48</v>
       </c>
       <c r="Y65">
-        <v>795</v>
+        <v>7578</v>
       </c>
       <c r="Z65">
-        <v>353.72899999999998</v>
-      </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+        <v>360.99099999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F66">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="G66" s="2">
         <v>45297</v>
@@ -5570,78 +5578,75 @@
         <v>20</v>
       </c>
       <c r="I66">
-        <v>20.95</v>
+        <v>21.26</v>
       </c>
       <c r="J66">
-        <v>11.23</v>
+        <v>10.67</v>
       </c>
       <c r="K66">
-        <v>536.038186157518</v>
+        <v>501.88146754468482</v>
       </c>
       <c r="L66">
-        <v>0.46116666666666672</v>
+        <v>0.47449999999999992</v>
       </c>
       <c r="M66">
-        <v>1.2878287478519199</v>
+        <v>1.37324190064457</v>
       </c>
       <c r="N66">
-        <v>503.28930000000003</v>
+        <v>501.64886000000013</v>
       </c>
       <c r="O66">
-        <v>12.23794</v>
+        <v>11.83794</v>
       </c>
       <c r="P66">
-        <v>0.39355299933867161</v>
+        <v>0.39494399378970019</v>
       </c>
       <c r="Q66">
-        <v>4.5428346180792799E-2</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>0.63968134587988124</v>
+        <v>0.59773040009628187</v>
       </c>
       <c r="S66">
-        <v>6.9280164905773392E-2</v>
+        <v>4.0156782830422129E-2</v>
       </c>
       <c r="T66">
-        <v>4.2267172700232312</v>
+        <v>3.8796790720398611</v>
       </c>
       <c r="U66">
-        <v>0.72163573263720604</v>
+        <v>1.080636963642936</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>7.5892213728818658E-2</v>
       </c>
       <c r="W66">
-        <v>0.92661537699513896</v>
+        <v>0.88961263793631462</v>
       </c>
       <c r="X66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y66">
+        <v>795</v>
+      </c>
+      <c r="Z66">
+        <v>353.72899999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67">
         <v>798</v>
-      </c>
-      <c r="Z66">
-        <v>388.66899999999998</v>
-      </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>1</v>
-      </c>
-      <c r="B67" t="s">
-        <v>26</v>
-      </c>
-      <c r="C67" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" t="s">
-        <v>31</v>
-      </c>
-      <c r="E67">
-        <v>5812</v>
-      </c>
-      <c r="F67">
-        <v>72</v>
       </c>
       <c r="G67" s="2">
         <v>45297</v>
@@ -5650,537 +5655,558 @@
         <v>20</v>
       </c>
       <c r="I67">
+        <v>20.95</v>
+      </c>
+      <c r="J67">
+        <v>11.23</v>
+      </c>
+      <c r="K67">
+        <v>536.038186157518</v>
+      </c>
+      <c r="L67">
+        <v>0.46116666666666672</v>
+      </c>
+      <c r="M67">
+        <v>1.2878287478519199</v>
+      </c>
+      <c r="N67">
+        <v>503.28930000000003</v>
+      </c>
+      <c r="O67">
+        <v>12.23794</v>
+      </c>
+      <c r="P67">
+        <v>0.39355299933867161</v>
+      </c>
+      <c r="Q67">
+        <v>4.5428346180792799E-2</v>
+      </c>
+      <c r="R67">
+        <v>0.63968134587988124</v>
+      </c>
+      <c r="S67">
+        <v>6.9280164905773392E-2</v>
+      </c>
+      <c r="T67">
+        <v>4.2267172700232312</v>
+      </c>
+      <c r="U67">
+        <v>0.72163573263720604</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.92661537699513896</v>
+      </c>
+      <c r="X67" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y67">
+        <v>798</v>
+      </c>
+      <c r="Z67">
+        <v>388.66899999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68">
+        <v>5812</v>
+      </c>
+      <c r="F68">
+        <v>72</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45297</v>
+      </c>
+      <c r="H68">
+        <v>20</v>
+      </c>
+      <c r="I68">
         <v>21.71</v>
       </c>
-      <c r="J67">
+      <c r="J68">
         <v>11.4</v>
       </c>
-      <c r="K67">
+      <c r="K68">
         <v>525.10363887609401</v>
       </c>
-      <c r="L67">
+      <c r="L68">
         <v>0.49299999999999988</v>
       </c>
-      <c r="M67">
+      <c r="M68">
         <v>1.369263027067273</v>
       </c>
-      <c r="N67">
+      <c r="N68">
         <v>502.02517999999998</v>
       </c>
-      <c r="O67">
+      <c r="O68">
         <v>11.75361</v>
       </c>
-      <c r="P67">
+      <c r="P68">
         <v>0.33014606736107749</v>
       </c>
-      <c r="Q67">
+      <c r="Q68">
         <v>0.1763737041152352</v>
       </c>
-      <c r="R67">
+      <c r="R68">
         <v>0.73340097018847228</v>
       </c>
-      <c r="S67">
+      <c r="S68">
         <v>4.6864030886039659E-2</v>
       </c>
-      <c r="T67">
+      <c r="T68">
         <v>2.696832020177923</v>
       </c>
-      <c r="U67">
+      <c r="U68">
         <v>0.96770411982522442</v>
       </c>
-      <c r="V67">
+      <c r="V68">
         <v>0.13834216083114459</v>
       </c>
-      <c r="W67">
+      <c r="W68">
         <v>0.81763505674294579</v>
       </c>
-      <c r="Y67">
+      <c r="Y68">
         <v>5812</v>
       </c>
-      <c r="Z67">
+      <c r="Z68">
         <v>367.36099999999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>2</v>
-      </c>
-      <c r="B68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="AA68" t="s">
         <v>30</v>
       </c>
-      <c r="D68" t="s">
-        <v>31</v>
-      </c>
-      <c r="E68">
-        <v>8386</v>
-      </c>
-      <c r="F68">
-        <v>229</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45274</v>
-      </c>
-      <c r="H68">
-        <v>20</v>
-      </c>
-      <c r="I68">
-        <v>16.36</v>
-      </c>
-      <c r="J68">
-        <v>8.15</v>
-      </c>
-      <c r="K68">
-        <v>498.16625916870419</v>
-      </c>
-      <c r="L68">
-        <v>0.42983333333333329</v>
-      </c>
-      <c r="M68">
-        <v>1.573511870701872</v>
-      </c>
-      <c r="N68">
-        <v>495.25391000000002</v>
-      </c>
-      <c r="O68">
-        <v>10.61383</v>
-      </c>
-      <c r="P68">
-        <v>1.6639486882007619</v>
-      </c>
-      <c r="Q68">
-        <v>4.8213523737098092E-2</v>
-      </c>
-      <c r="R68">
-        <v>1.0199520795766499</v>
-      </c>
-      <c r="S68">
-        <v>0.1859011534680198</v>
-      </c>
-      <c r="T68">
-        <v>3.898323585321827</v>
-      </c>
-      <c r="U68">
-        <v>1.2965337145611719</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0.1187170264663293</v>
-      </c>
-      <c r="Y68">
-        <v>8386</v>
-      </c>
-      <c r="Z68">
-        <v>270.44099999999997</v>
-      </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2</v>
       </c>
       <c r="B69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" t="s">
         <v>32</v>
       </c>
-      <c r="C69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" t="s">
-        <v>28</v>
-      </c>
       <c r="E69">
-        <v>7922</v>
+        <v>8386</v>
       </c>
       <c r="F69">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="G69" s="2">
-        <v>45269</v>
+        <v>45274</v>
       </c>
       <c r="H69">
         <v>20</v>
       </c>
       <c r="I69">
-        <v>54.78</v>
+        <v>16.36</v>
       </c>
       <c r="J69">
-        <v>22.61</v>
+        <v>8.15</v>
       </c>
       <c r="K69">
-        <v>412.7418765972983</v>
+        <v>498.16625916870419</v>
       </c>
       <c r="L69">
-        <v>0.63350000000000006</v>
+        <v>0.42983333333333329</v>
       </c>
       <c r="M69">
-        <v>1.7414203356638209</v>
+        <v>1.573511870701872</v>
       </c>
       <c r="N69">
-        <v>510.98811999999998</v>
+        <v>495.25391000000002</v>
       </c>
       <c r="O69">
-        <v>11.42821</v>
+        <v>10.61383</v>
       </c>
       <c r="P69">
-        <v>1.1901309632997139</v>
+        <v>1.6639486882007619</v>
       </c>
       <c r="Q69">
-        <v>2.0059303297881779E-2</v>
+        <v>4.8213523737098092E-2</v>
       </c>
       <c r="R69">
-        <v>5.3739881758489556</v>
+        <v>1.0199520795766499</v>
       </c>
       <c r="S69">
-        <v>3.1370710636721442E-2</v>
+        <v>0.1859011534680198</v>
       </c>
       <c r="T69">
-        <v>5.5473002762596</v>
+        <v>3.898323585321827</v>
       </c>
       <c r="U69">
-        <v>2.0319620672428358</v>
+        <v>1.2965337145611719</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>0.1187170264663293</v>
       </c>
       <c r="Y69">
-        <v>7922</v>
+        <v>8386</v>
       </c>
       <c r="Z69">
-        <v>633.245</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+        <v>270.44099999999997</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E70">
-        <v>9084</v>
+        <v>7922</v>
       </c>
       <c r="F70">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G70" s="2">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="H70">
         <v>20</v>
       </c>
       <c r="I70">
-        <v>18.91</v>
+        <v>54.78</v>
       </c>
       <c r="J70">
-        <v>9.6999999999999993</v>
+        <v>22.61</v>
       </c>
       <c r="K70">
-        <v>512.95610787942883</v>
+        <v>412.7418765972983</v>
       </c>
       <c r="L70">
-        <v>0.46500000000000002</v>
+        <v>0.63350000000000006</v>
       </c>
       <c r="M70">
-        <v>1.6154226723827381</v>
+        <v>1.7414203356638209</v>
       </c>
       <c r="N70">
-        <v>494.04324000000003</v>
+        <v>510.98811999999998</v>
       </c>
       <c r="O70">
-        <v>10.16873</v>
+        <v>11.42821</v>
       </c>
       <c r="P70">
-        <v>1.1160516200863519</v>
+        <v>1.1901309632997139</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.0059303297881779E-2</v>
       </c>
       <c r="R70">
-        <v>0.7522171731924191</v>
+        <v>5.3739881758489556</v>
       </c>
       <c r="S70">
-        <v>1.9512164590487269E-2</v>
+        <v>3.1370710636721442E-2</v>
       </c>
       <c r="T70">
-        <v>2.8413691722536489</v>
+        <v>5.5473002762596</v>
       </c>
       <c r="U70">
-        <v>1.2709356560402161</v>
+        <v>2.0319620672428358</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.61768589198639712</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>9084</v>
+        <v>7922</v>
       </c>
       <c r="Z70">
-        <v>344.25900000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+        <v>633.245</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2</v>
       </c>
       <c r="B71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" t="s">
         <v>32</v>
       </c>
-      <c r="C71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D71" t="s">
-        <v>28</v>
-      </c>
       <c r="E71">
-        <v>7924</v>
+        <v>9084</v>
       </c>
       <c r="F71">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G71" s="2">
-        <v>45269</v>
+        <v>45268</v>
       </c>
       <c r="H71">
         <v>20</v>
       </c>
       <c r="I71">
-        <v>49.75</v>
+        <v>18.91</v>
       </c>
       <c r="J71">
-        <v>20.18</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K71">
-        <v>405.6281407035176</v>
+        <v>512.95610787942883</v>
       </c>
       <c r="L71">
-        <v>0.44216666666666671</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="M71">
-        <v>1.4830588113779779</v>
+        <v>1.6154226723827381</v>
       </c>
       <c r="N71">
-        <v>515.84793000000002</v>
+        <v>494.04324000000003</v>
       </c>
       <c r="O71">
-        <v>12.21218</v>
+        <v>10.16873</v>
       </c>
       <c r="P71">
-        <v>1.2945568975946811</v>
+        <v>1.1160516200863519</v>
       </c>
       <c r="Q71">
-        <v>0.14270561841023541</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>6.0071503049038597</v>
+        <v>0.7522171731924191</v>
       </c>
       <c r="S71">
-        <v>7.3227407119202947E-3</v>
+        <v>1.9512164590487269E-2</v>
       </c>
       <c r="T71">
-        <v>3.9968266209594798</v>
+        <v>2.8413691722536489</v>
       </c>
       <c r="U71">
-        <v>2.3473002493592201</v>
+        <v>1.2709356560402161</v>
       </c>
       <c r="V71">
-        <v>3.4173650973809977E-2</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>0.62042971834260663</v>
+        <v>0.61768589198639712</v>
       </c>
       <c r="Y71">
-        <v>7924</v>
+        <v>9084</v>
       </c>
       <c r="Z71">
-        <v>876.08899999999994</v>
-      </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+        <v>344.25900000000001</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2</v>
       </c>
       <c r="B72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72">
+        <v>7924</v>
+      </c>
+      <c r="F72">
+        <v>257</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45269</v>
+      </c>
+      <c r="H72">
+        <v>20</v>
+      </c>
+      <c r="I72">
+        <v>49.75</v>
+      </c>
+      <c r="J72">
+        <v>20.18</v>
+      </c>
+      <c r="K72">
+        <v>405.6281407035176</v>
+      </c>
+      <c r="L72">
+        <v>0.44216666666666671</v>
+      </c>
+      <c r="M72">
+        <v>1.4830588113779779</v>
+      </c>
+      <c r="N72">
+        <v>515.84793000000002</v>
+      </c>
+      <c r="O72">
+        <v>12.21218</v>
+      </c>
+      <c r="P72">
+        <v>1.2945568975946811</v>
+      </c>
+      <c r="Q72">
+        <v>0.14270561841023541</v>
+      </c>
+      <c r="R72">
+        <v>6.0071503049038597</v>
+      </c>
+      <c r="S72">
+        <v>7.3227407119202947E-3</v>
+      </c>
+      <c r="T72">
+        <v>3.9968266209594798</v>
+      </c>
+      <c r="U72">
+        <v>2.3473002493592201</v>
+      </c>
+      <c r="V72">
+        <v>3.4173650973809977E-2</v>
+      </c>
+      <c r="W72">
+        <v>0.62042971834260663</v>
+      </c>
+      <c r="Y72">
+        <v>7924</v>
+      </c>
+      <c r="Z72">
+        <v>876.08899999999994</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
         <v>32</v>
       </c>
-      <c r="C72" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" t="s">
-        <v>31</v>
-      </c>
-      <c r="E72">
+      <c r="E73">
         <v>8384</v>
       </c>
-      <c r="F72">
+      <c r="F73">
         <v>264</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G73" s="2">
         <v>45274</v>
       </c>
-      <c r="H72">
-        <v>20</v>
-      </c>
-      <c r="I72">
+      <c r="H73">
+        <v>20</v>
+      </c>
+      <c r="I73">
         <v>18.64</v>
       </c>
-      <c r="J72">
+      <c r="J73">
         <v>8.99</v>
       </c>
-      <c r="K72">
+      <c r="K73">
         <v>482.2961373390558</v>
       </c>
-      <c r="L72">
+      <c r="L73">
         <v>0.45816666666666661</v>
       </c>
-      <c r="M72">
+      <c r="M73">
         <v>1.556535343438737</v>
       </c>
-      <c r="N72">
+      <c r="N73">
         <v>494.53361999999998</v>
       </c>
-      <c r="O72">
+      <c r="O73">
         <v>10.093719999999999</v>
       </c>
-      <c r="P72">
+      <c r="P73">
         <v>2.5136852440698338</v>
       </c>
-      <c r="Q72">
+      <c r="Q73">
         <v>1.1931577182508131E-2</v>
       </c>
-      <c r="R72">
+      <c r="R73">
         <v>1.400912031658184</v>
       </c>
-      <c r="S72">
+      <c r="S73">
         <v>3.9400168357050673E-2</v>
       </c>
-      <c r="T72">
+      <c r="T73">
         <v>3.0017549988216121</v>
       </c>
-      <c r="U72">
+      <c r="U73">
         <v>1.641308584620546</v>
       </c>
-      <c r="V72">
+      <c r="V73">
         <v>0.13853481586475599</v>
       </c>
-      <c r="W72">
+      <c r="W73">
         <v>0.65062603499823901</v>
       </c>
-      <c r="Y72">
+      <c r="Y73">
         <v>8384</v>
       </c>
-      <c r="Z72">
+      <c r="Z73">
         <v>306.63299999999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>34</v>
-      </c>
-      <c r="C73" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73">
-        <v>8396</v>
-      </c>
-      <c r="F73">
-        <v>120</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45272</v>
-      </c>
-      <c r="H73">
-        <v>20</v>
-      </c>
-      <c r="I73">
-        <v>39.68</v>
-      </c>
-      <c r="J73">
-        <v>17.48</v>
-      </c>
-      <c r="K73">
-        <v>440.52419354838707</v>
-      </c>
-      <c r="L73">
-        <v>0.53599999999999992</v>
-      </c>
-      <c r="M73">
-        <v>1.6122395735209001</v>
-      </c>
-      <c r="N73">
-        <v>505.43601999999998</v>
-      </c>
-      <c r="O73">
-        <v>17.683140000000002</v>
-      </c>
-      <c r="P73">
-        <v>0.99599498213219884</v>
-      </c>
-      <c r="Q73">
-        <v>3.1515931325567653E-2</v>
-      </c>
-      <c r="R73">
-        <v>4.0436192109305251</v>
-      </c>
-      <c r="S73">
-        <v>1.6129719076343751E-2</v>
-      </c>
-      <c r="T73">
-        <v>5.0176051738926946</v>
-      </c>
-      <c r="U73">
-        <v>2.472863701896574</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0.65855079646455117</v>
-      </c>
-      <c r="Y73">
-        <v>8396</v>
-      </c>
-      <c r="Z73">
-        <v>597.89800000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E74">
-        <v>9090</v>
+        <v>8396</v>
       </c>
       <c r="F74">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G74" s="2">
         <v>45272</v>
@@ -6189,229 +6215,238 @@
         <v>20</v>
       </c>
       <c r="I74">
-        <v>35.29</v>
+        <v>39.68</v>
       </c>
       <c r="J74">
-        <v>17.72</v>
+        <v>17.48</v>
       </c>
       <c r="K74">
-        <v>502.12524794559363</v>
+        <v>440.52419354838707</v>
       </c>
       <c r="L74">
-        <v>0.46633333333333332</v>
+        <v>0.53599999999999992</v>
       </c>
       <c r="M74">
-        <v>1.62125835362944</v>
+        <v>1.6122395735209001</v>
       </c>
       <c r="N74">
-        <v>481.15814</v>
+        <v>505.43601999999998</v>
       </c>
       <c r="O74">
-        <v>10.626749999999999</v>
+        <v>17.683140000000002</v>
       </c>
       <c r="P74">
-        <v>0.42395812261181809</v>
+        <v>0.99599498213219884</v>
       </c>
       <c r="Q74">
-        <v>7.9852399398745895E-3</v>
+        <v>3.1515931325567653E-2</v>
       </c>
       <c r="R74">
-        <v>0.59408276145039784</v>
+        <v>4.0436192109305251</v>
       </c>
       <c r="S74">
-        <v>5.3337140772252416E-3</v>
+        <v>1.6129719076343751E-2</v>
       </c>
       <c r="T74">
-        <v>3.93642184694286</v>
+        <v>5.0176051738926946</v>
       </c>
       <c r="U74">
-        <v>1.007553180000579</v>
+        <v>2.472863701896574</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.4689857381470891</v>
+        <v>0.65855079646455117</v>
       </c>
       <c r="Y74">
+        <v>8396</v>
+      </c>
+      <c r="Z74">
+        <v>597.89800000000002</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" t="s">
+        <v>31</v>
+      </c>
+      <c r="D75" t="s">
+        <v>32</v>
+      </c>
+      <c r="E75">
         <v>9090</v>
       </c>
-      <c r="Z74">
-        <v>618.99599999999998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>4</v>
-      </c>
-      <c r="B75" t="s">
-        <v>36</v>
-      </c>
-      <c r="C75" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" t="s">
-        <v>31</v>
-      </c>
-      <c r="E75">
-        <v>5807</v>
-      </c>
       <c r="F75">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="G75" s="2">
-        <v>45273</v>
+        <v>45272</v>
       </c>
       <c r="H75">
         <v>20</v>
       </c>
       <c r="I75">
-        <v>33.79</v>
+        <v>35.29</v>
       </c>
       <c r="J75">
-        <v>15.51</v>
+        <v>17.72</v>
       </c>
       <c r="K75">
-        <v>459.01154187629481</v>
+        <v>502.12524794559363</v>
       </c>
       <c r="L75">
-        <v>0.48666666666666669</v>
+        <v>0.46633333333333332</v>
       </c>
       <c r="M75">
-        <v>1.5939367550653321</v>
+        <v>1.62125835362944</v>
       </c>
       <c r="N75">
-        <v>504.64733000000001</v>
+        <v>481.15814</v>
       </c>
       <c r="O75">
-        <v>11.50465</v>
+        <v>10.626749999999999</v>
       </c>
       <c r="P75">
-        <v>1.2409842903384321</v>
+        <v>0.42395812261181809</v>
       </c>
       <c r="Q75">
-        <v>6.9328453469162082E-2</v>
+        <v>7.9852399398745895E-3</v>
       </c>
       <c r="R75">
-        <v>0.77670988526236651</v>
+        <v>0.59408276145039784</v>
       </c>
       <c r="S75">
-        <v>3.0715362206706572E-2</v>
+        <v>5.3337140772252416E-3</v>
       </c>
       <c r="T75">
-        <v>2.247079346959028</v>
+        <v>3.93642184694286</v>
       </c>
       <c r="U75">
-        <v>1.953110876177266</v>
+        <v>1.007553180000579</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
+        <v>0.4689857381470891</v>
+      </c>
+      <c r="Y75">
+        <v>9090</v>
+      </c>
+      <c r="Z75">
+        <v>618.99599999999998</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76">
+        <v>5807</v>
+      </c>
+      <c r="F76">
+        <v>217</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45273</v>
+      </c>
+      <c r="H76">
+        <v>20</v>
+      </c>
+      <c r="I76">
+        <v>33.79</v>
+      </c>
+      <c r="J76">
+        <v>15.51</v>
+      </c>
+      <c r="K76">
+        <v>459.01154187629481</v>
+      </c>
+      <c r="L76">
+        <v>0.48666666666666669</v>
+      </c>
+      <c r="M76">
+        <v>1.5939367550653321</v>
+      </c>
+      <c r="N76">
+        <v>504.64733000000001</v>
+      </c>
+      <c r="O76">
+        <v>11.50465</v>
+      </c>
+      <c r="P76">
+        <v>1.2409842903384321</v>
+      </c>
+      <c r="Q76">
+        <v>6.9328453469162082E-2</v>
+      </c>
+      <c r="R76">
+        <v>0.77670988526236651</v>
+      </c>
+      <c r="S76">
+        <v>3.0715362206706572E-2</v>
+      </c>
+      <c r="T76">
+        <v>2.247079346959028</v>
+      </c>
+      <c r="U76">
+        <v>1.953110876177266</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
         <v>0.75758155635406643</v>
       </c>
-      <c r="Y75">
+      <c r="Y76">
         <v>5807</v>
       </c>
-      <c r="Z75">
+      <c r="Z76">
         <v>559.16999999999996</v>
       </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>6</v>
-      </c>
-      <c r="B76" t="s">
-        <v>34</v>
-      </c>
-      <c r="C76" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" t="s">
-        <v>31</v>
-      </c>
-      <c r="E76">
-        <v>8381</v>
-      </c>
-      <c r="F76">
-        <v>282</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45275</v>
-      </c>
-      <c r="H76">
-        <v>20</v>
-      </c>
-      <c r="I76">
-        <v>21.39</v>
-      </c>
-      <c r="J76">
-        <v>9.65</v>
-      </c>
-      <c r="K76">
-        <v>451.14539504441319</v>
-      </c>
-      <c r="L76">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="M76">
-        <v>1.578551777233115</v>
-      </c>
-      <c r="N76">
-        <v>501.29680999999999</v>
-      </c>
-      <c r="O76">
-        <v>12.204420000000001</v>
-      </c>
-      <c r="P76">
-        <v>0.4225314752105393</v>
-      </c>
-      <c r="Q76">
-        <v>4.8980220744282037E-2</v>
-      </c>
-      <c r="R76">
-        <v>1.317943575072541</v>
-      </c>
-      <c r="S76">
-        <v>4.113122169495239E-2</v>
-      </c>
-      <c r="T76">
-        <v>4.6592782608710079</v>
-      </c>
-      <c r="U76">
-        <v>1.281243421290333</v>
-      </c>
-      <c r="V76">
-        <v>3.587299286256472E-2</v>
-      </c>
-      <c r="W76">
-        <v>0.77492717217704943</v>
-      </c>
-      <c r="Y76">
-        <v>8381</v>
-      </c>
-      <c r="Z76">
-        <v>358.34199999999998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E77">
-        <v>4905</v>
+        <v>8381</v>
       </c>
       <c r="F77">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="G77" s="2">
         <v>45275</v>
@@ -6420,75 +6455,78 @@
         <v>20</v>
       </c>
       <c r="I77">
-        <v>22.56</v>
+        <v>21.39</v>
       </c>
       <c r="J77">
-        <v>10.65</v>
+        <v>9.65</v>
       </c>
       <c r="K77">
-        <v>472.07446808510639</v>
+        <v>451.14539504441319</v>
       </c>
       <c r="L77">
-        <v>0.4971666666666667</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="M77">
-        <v>1.63717384793863</v>
+        <v>1.578551777233115</v>
       </c>
       <c r="N77">
-        <v>501.09469999999999</v>
+        <v>501.29680999999999</v>
       </c>
       <c r="O77">
-        <v>11.67764</v>
+        <v>12.204420000000001</v>
       </c>
       <c r="P77">
-        <v>0.46950827267490092</v>
+        <v>0.4225314752105393</v>
       </c>
       <c r="Q77">
-        <v>3.8620375180083738E-2</v>
+        <v>4.8980220744282037E-2</v>
       </c>
       <c r="R77">
-        <v>1.166290508501086</v>
+        <v>1.317943575072541</v>
       </c>
       <c r="S77">
-        <v>4.6923740594414988E-2</v>
+        <v>4.113122169495239E-2</v>
       </c>
       <c r="T77">
-        <v>2.4248670528247889</v>
+        <v>4.6592782608710079</v>
       </c>
       <c r="U77">
-        <v>1.3409998607212761</v>
+        <v>1.281243421290333</v>
       </c>
       <c r="V77">
-        <v>7.3747026661911325E-2</v>
+        <v>3.587299286256472E-2</v>
       </c>
       <c r="W77">
-        <v>0.76572559903469151</v>
+        <v>0.77492717217704943</v>
       </c>
       <c r="Y77">
+        <v>8381</v>
+      </c>
+      <c r="Z77">
+        <v>358.34199999999998</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78">
         <v>4905</v>
       </c>
-      <c r="Z77">
-        <v>380.87099999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>7</v>
-      </c>
-      <c r="B78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" t="s">
-        <v>31</v>
-      </c>
-      <c r="E78">
-        <v>6992</v>
-      </c>
       <c r="F78">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="G78" s="2">
         <v>45275</v>
@@ -6497,306 +6535,318 @@
         <v>20</v>
       </c>
       <c r="I78">
+        <v>22.56</v>
+      </c>
+      <c r="J78">
+        <v>10.65</v>
+      </c>
+      <c r="K78">
+        <v>472.07446808510639</v>
+      </c>
+      <c r="L78">
+        <v>0.4971666666666667</v>
+      </c>
+      <c r="M78">
+        <v>1.63717384793863</v>
+      </c>
+      <c r="N78">
+        <v>501.09469999999999</v>
+      </c>
+      <c r="O78">
+        <v>11.67764</v>
+      </c>
+      <c r="P78">
+        <v>0.46950827267490092</v>
+      </c>
+      <c r="Q78">
+        <v>3.8620375180083738E-2</v>
+      </c>
+      <c r="R78">
+        <v>1.166290508501086</v>
+      </c>
+      <c r="S78">
+        <v>4.6923740594414988E-2</v>
+      </c>
+      <c r="T78">
+        <v>2.4248670528247889</v>
+      </c>
+      <c r="U78">
+        <v>1.3409998607212761</v>
+      </c>
+      <c r="V78">
+        <v>7.3747026661911325E-2</v>
+      </c>
+      <c r="W78">
+        <v>0.76572559903469151</v>
+      </c>
+      <c r="Y78">
+        <v>4905</v>
+      </c>
+      <c r="Z78">
+        <v>380.87099999999998</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" t="s">
+        <v>32</v>
+      </c>
+      <c r="E79">
+        <v>6992</v>
+      </c>
+      <c r="F79">
+        <v>351</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45275</v>
+      </c>
+      <c r="H79">
+        <v>20</v>
+      </c>
+      <c r="I79">
         <v>14.18</v>
       </c>
-      <c r="J78">
+      <c r="J79">
         <v>6.58</v>
       </c>
-      <c r="K78">
+      <c r="K79">
         <v>464.03385049365301</v>
       </c>
-      <c r="L78">
+      <c r="L79">
         <v>0.45116666666666672</v>
       </c>
-      <c r="M78">
+      <c r="M79">
         <v>1.573246612463385</v>
       </c>
-      <c r="N78">
+      <c r="N79">
         <v>497.12306999999998</v>
       </c>
-      <c r="O78">
+      <c r="O79">
         <v>10.16024</v>
       </c>
-      <c r="P78">
+      <c r="P79">
         <v>0.4436594649764164</v>
       </c>
-      <c r="Q78">
+      <c r="Q79">
         <v>6.8034439227985494E-2</v>
       </c>
-      <c r="R78">
+      <c r="R79">
         <v>0.99922436569322559</v>
       </c>
-      <c r="S78">
+      <c r="S79">
         <v>3.9521345769629727E-2</v>
       </c>
-      <c r="T78">
+      <c r="T79">
         <v>4.9690562418409971</v>
       </c>
-      <c r="U78">
+      <c r="U79">
         <v>0.9580686381773037</v>
       </c>
-      <c r="V78">
+      <c r="V79">
         <v>2.051497620042958E-2</v>
       </c>
-      <c r="W78">
+      <c r="W79">
         <v>0.63895894341543069</v>
       </c>
-      <c r="Y78">
+      <c r="Y79">
         <v>6992</v>
       </c>
-      <c r="Z78">
+      <c r="Z79">
         <v>250.54300000000001</v>
       </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="AA79" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>8</v>
       </c>
-      <c r="B79" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="B80" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="E79">
+      <c r="D80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80">
         <v>7237</v>
       </c>
-      <c r="F79">
+      <c r="F80">
         <v>384</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G80" s="2">
         <v>45276</v>
       </c>
-      <c r="H79">
-        <v>20</v>
-      </c>
-      <c r="I79">
+      <c r="H80">
+        <v>20</v>
+      </c>
+      <c r="I80">
         <v>44.74</v>
       </c>
-      <c r="J79">
+      <c r="J80">
         <v>19.57</v>
       </c>
-      <c r="K79">
+      <c r="K80">
         <v>437.41618238712562</v>
       </c>
-      <c r="L79">
+      <c r="L80">
         <v>0.62883333333333324</v>
       </c>
-      <c r="M79">
+      <c r="M80">
         <v>2.0438147275384231</v>
       </c>
-      <c r="N79">
+      <c r="N80">
         <v>512.32413999999994</v>
       </c>
-      <c r="O79">
+      <c r="O80">
         <v>12.007250000000001</v>
       </c>
-      <c r="P79">
+      <c r="P80">
         <v>1.336143849681799</v>
       </c>
-      <c r="Q79">
+      <c r="Q80">
         <v>3.0112866382734651E-3</v>
       </c>
-      <c r="R79">
+      <c r="R80">
         <v>5.0191036639964466</v>
       </c>
-      <c r="S79">
+      <c r="S80">
         <v>2.5242743593243942E-2</v>
       </c>
-      <c r="T79">
+      <c r="T80">
         <v>3.6844152724048582</v>
       </c>
-      <c r="U79">
+      <c r="U80">
         <v>2.8787395747135962</v>
-      </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
-      <c r="W79">
-        <v>0.7703790828992938</v>
-      </c>
-      <c r="Y79">
-        <v>7237</v>
-      </c>
-      <c r="Z79">
-        <v>576.95299999999997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>36</v>
-      </c>
-      <c r="C80" t="s">
-        <v>27</v>
-      </c>
-      <c r="D80" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80">
-        <v>8361</v>
-      </c>
-      <c r="F80">
-        <v>446</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45280</v>
-      </c>
-      <c r="H80">
-        <v>20</v>
-      </c>
-      <c r="I80">
-        <v>26.61</v>
-      </c>
-      <c r="J80">
-        <v>11.51</v>
-      </c>
-      <c r="K80">
-        <v>432.54415633220589</v>
-      </c>
-      <c r="L80">
-        <v>0.53949999999999998</v>
-      </c>
-      <c r="M80">
-        <v>1.317802928800893</v>
-      </c>
-      <c r="N80">
-        <v>517.37492000000009</v>
-      </c>
-      <c r="O80">
-        <v>12.86652</v>
-      </c>
-      <c r="P80">
-        <v>1.264200753020895</v>
-      </c>
-      <c r="Q80">
-        <v>6.1479881160042887E-3</v>
-      </c>
-      <c r="R80">
-        <v>3.5627477103693201</v>
-      </c>
-      <c r="S80">
-        <v>1.148773473730965E-2</v>
-      </c>
-      <c r="T80">
-        <v>5.0766016442802009</v>
-      </c>
-      <c r="U80">
-        <v>1.668584278384468</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.48285890770807932</v>
+        <v>0.7703790828992938</v>
       </c>
       <c r="Y80">
-        <v>8361</v>
+        <v>7237</v>
       </c>
       <c r="Z80">
-        <v>431.43200000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+        <v>576.95299999999997</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E81">
-        <v>4469</v>
+        <v>8361</v>
       </c>
       <c r="F81">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="G81" s="2">
-        <v>45281</v>
+        <v>45280</v>
       </c>
       <c r="H81">
         <v>20</v>
       </c>
       <c r="I81">
-        <v>42.26</v>
+        <v>26.61</v>
       </c>
       <c r="J81">
-        <v>17.13</v>
+        <v>11.51</v>
       </c>
       <c r="K81">
-        <v>405.34784666351158</v>
+        <v>432.54415633220589</v>
       </c>
       <c r="L81">
-        <v>0.53433333333333333</v>
+        <v>0.53949999999999998</v>
       </c>
       <c r="M81">
-        <v>1.4979132727332221</v>
+        <v>1.317802928800893</v>
       </c>
       <c r="N81">
-        <v>487.83427999999998</v>
+        <v>517.37492000000009</v>
       </c>
       <c r="O81">
-        <v>13.06237</v>
+        <v>12.86652</v>
       </c>
       <c r="P81">
-        <v>1.549984801394928</v>
+        <v>1.264200753020895</v>
       </c>
       <c r="Q81">
-        <v>2.4285866738629701E-3</v>
+        <v>6.1479881160042887E-3</v>
       </c>
       <c r="R81">
-        <v>3.804837808989892</v>
+        <v>3.5627477103693201</v>
       </c>
       <c r="S81">
-        <v>4.1963211958589507E-2</v>
+        <v>1.148773473730965E-2</v>
       </c>
       <c r="T81">
-        <v>6.439243411095946</v>
+        <v>5.0766016442802009</v>
       </c>
       <c r="U81">
-        <v>2.100718081409044</v>
+        <v>1.668584278384468</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.70382998236833993</v>
+        <v>0.48285890770807932</v>
       </c>
       <c r="Y81">
+        <v>8361</v>
+      </c>
+      <c r="Z81">
+        <v>431.43200000000002</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82">
         <v>4469</v>
       </c>
-      <c r="Z81">
-        <v>670.822</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>11</v>
-      </c>
-      <c r="B82" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" t="s">
-        <v>30</v>
-      </c>
-      <c r="D82" t="s">
-        <v>31</v>
-      </c>
-      <c r="E82">
-        <v>4898</v>
-      </c>
       <c r="F82">
-        <v>573</v>
+        <v>458</v>
       </c>
       <c r="G82" s="2">
         <v>45281</v>
@@ -6805,152 +6855,158 @@
         <v>20</v>
       </c>
       <c r="I82">
-        <v>24.37</v>
+        <v>42.26</v>
       </c>
       <c r="J82">
-        <v>12.12</v>
+        <v>17.13</v>
       </c>
       <c r="K82">
-        <v>497.33278621255641</v>
+        <v>405.34784666351158</v>
       </c>
       <c r="L82">
-        <v>0.48316666666666669</v>
+        <v>0.53433333333333333</v>
       </c>
       <c r="M82">
-        <v>1.5459250138992771</v>
+        <v>1.4979132727332221</v>
       </c>
       <c r="N82">
-        <v>486.76823000000002</v>
+        <v>487.83427999999998</v>
       </c>
       <c r="O82">
-        <v>10.291040000000001</v>
+        <v>13.06237</v>
       </c>
       <c r="P82">
-        <v>1.433819373048095</v>
+        <v>1.549984801394928</v>
       </c>
       <c r="Q82">
-        <v>3.6403192930293718E-2</v>
+        <v>2.4285866738629701E-3</v>
       </c>
       <c r="R82">
-        <v>0.63406200116279854</v>
+        <v>3.804837808989892</v>
       </c>
       <c r="S82">
-        <v>5.5330553409560959E-2</v>
+        <v>4.1963211958589507E-2</v>
       </c>
       <c r="T82">
-        <v>3.7877128456906521</v>
+        <v>6.439243411095946</v>
       </c>
       <c r="U82">
-        <v>1.301339676512913</v>
+        <v>2.100718081409044</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
+        <v>0.70382998236833993</v>
+      </c>
+      <c r="Y82">
+        <v>4469</v>
+      </c>
+      <c r="Z82">
+        <v>670.822</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>11</v>
+      </c>
+      <c r="B83" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" t="s">
+        <v>32</v>
+      </c>
+      <c r="E83">
+        <v>4898</v>
+      </c>
+      <c r="F83">
+        <v>573</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45281</v>
+      </c>
+      <c r="H83">
+        <v>20</v>
+      </c>
+      <c r="I83">
+        <v>24.37</v>
+      </c>
+      <c r="J83">
+        <v>12.12</v>
+      </c>
+      <c r="K83">
+        <v>497.33278621255641</v>
+      </c>
+      <c r="L83">
+        <v>0.48316666666666669</v>
+      </c>
+      <c r="M83">
+        <v>1.5459250138992771</v>
+      </c>
+      <c r="N83">
+        <v>486.76823000000002</v>
+      </c>
+      <c r="O83">
+        <v>10.291040000000001</v>
+      </c>
+      <c r="P83">
+        <v>1.433819373048095</v>
+      </c>
+      <c r="Q83">
+        <v>3.6403192930293718E-2</v>
+      </c>
+      <c r="R83">
+        <v>0.63406200116279854</v>
+      </c>
+      <c r="S83">
+        <v>5.5330553409560959E-2</v>
+      </c>
+      <c r="T83">
+        <v>3.7877128456906521</v>
+      </c>
+      <c r="U83">
+        <v>1.301339676512913</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
         <v>1.0481090106853319</v>
       </c>
-      <c r="Y82">
+      <c r="Y83">
         <v>4898</v>
       </c>
-      <c r="Z82">
+      <c r="Z83">
         <v>417.17200000000003</v>
       </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>12</v>
-      </c>
-      <c r="B83" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83">
-        <v>4894</v>
-      </c>
-      <c r="F83">
-        <v>713</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45283</v>
-      </c>
-      <c r="H83">
-        <v>20</v>
-      </c>
-      <c r="I83">
-        <v>29.97</v>
-      </c>
-      <c r="J83">
-        <v>13.32</v>
-      </c>
-      <c r="K83">
-        <v>444.44444444444451</v>
-      </c>
-      <c r="L83">
-        <v>0.56933333333333336</v>
-      </c>
-      <c r="M83">
-        <v>1.804817054662093</v>
-      </c>
-      <c r="N83">
-        <v>521.19670999999994</v>
-      </c>
-      <c r="O83">
-        <v>12.062939999999999</v>
-      </c>
-      <c r="P83">
-        <v>0.82856712256177656</v>
-      </c>
-      <c r="Q83">
-        <v>1.614116365969542E-2</v>
-      </c>
-      <c r="R83">
-        <v>4.5613781908183162</v>
-      </c>
-      <c r="S83">
-        <v>4.7234070033405358E-2</v>
-      </c>
-      <c r="T83">
-        <v>3.7633420068685202</v>
-      </c>
-      <c r="U83">
-        <v>2.2129816549622912</v>
-      </c>
-      <c r="V83">
-        <v>4.7647415977878652E-2</v>
-      </c>
-      <c r="W83">
-        <v>0.6999223603805288</v>
-      </c>
-      <c r="Y83">
-        <v>4894</v>
-      </c>
-      <c r="Z83">
-        <v>427.81799999999998</v>
-      </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA83" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E84">
-        <v>7594</v>
+        <v>4894</v>
       </c>
       <c r="F84">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G84" s="2">
         <v>45283</v>
@@ -6959,383 +7015,398 @@
         <v>20</v>
       </c>
       <c r="I84">
+        <v>29.97</v>
+      </c>
+      <c r="J84">
+        <v>13.32</v>
+      </c>
+      <c r="K84">
+        <v>444.44444444444451</v>
+      </c>
+      <c r="L84">
+        <v>0.56933333333333336</v>
+      </c>
+      <c r="M84">
+        <v>1.804817054662093</v>
+      </c>
+      <c r="N84">
+        <v>521.19670999999994</v>
+      </c>
+      <c r="O84">
+        <v>12.062939999999999</v>
+      </c>
+      <c r="P84">
+        <v>0.82856712256177656</v>
+      </c>
+      <c r="Q84">
+        <v>1.614116365969542E-2</v>
+      </c>
+      <c r="R84">
+        <v>4.5613781908183162</v>
+      </c>
+      <c r="S84">
+        <v>4.7234070033405358E-2</v>
+      </c>
+      <c r="T84">
+        <v>3.7633420068685202</v>
+      </c>
+      <c r="U84">
+        <v>2.2129816549622912</v>
+      </c>
+      <c r="V84">
+        <v>4.7647415977878652E-2</v>
+      </c>
+      <c r="W84">
+        <v>0.6999223603805288</v>
+      </c>
+      <c r="Y84">
+        <v>4894</v>
+      </c>
+      <c r="Z84">
+        <v>427.81799999999998</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85">
+        <v>7594</v>
+      </c>
+      <c r="F85">
+        <v>714</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45283</v>
+      </c>
+      <c r="H85">
+        <v>20</v>
+      </c>
+      <c r="I85">
         <v>34.950000000000003</v>
       </c>
-      <c r="J84">
+      <c r="J85">
         <v>15.19</v>
       </c>
-      <c r="K84">
+      <c r="K85">
         <v>434.62088698140201</v>
       </c>
-      <c r="L84">
+      <c r="L85">
         <v>0.58466666666666667</v>
       </c>
-      <c r="M84">
+      <c r="M85">
         <v>1.645927369808684</v>
       </c>
-      <c r="N84">
+      <c r="N85">
         <v>520.02067999999997</v>
       </c>
-      <c r="O84">
+      <c r="O85">
         <v>15.24436</v>
       </c>
-      <c r="P84">
+      <c r="P85">
         <v>1.0606810810614751</v>
       </c>
-      <c r="Q84">
+      <c r="Q85">
         <v>3.2561942362806899E-2</v>
       </c>
-      <c r="R84">
+      <c r="R85">
         <v>2.8918165898468282</v>
       </c>
-      <c r="S84">
+      <c r="S85">
         <v>2.768839215525221E-2</v>
       </c>
-      <c r="T84">
+      <c r="T85">
         <v>5.3347076986564579</v>
       </c>
-      <c r="U84">
+      <c r="U85">
         <v>2.029258417161623</v>
       </c>
-      <c r="V84">
+      <c r="V85">
         <v>3.0498732099151851E-2</v>
       </c>
-      <c r="W84">
+      <c r="W85">
         <v>0.71251690656074285</v>
       </c>
-      <c r="Y84">
+      <c r="Y85">
         <v>7594</v>
       </c>
-      <c r="Z84">
+      <c r="Z85">
         <v>482.79700000000003</v>
       </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="AA85" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>13</v>
       </c>
-      <c r="B85" t="s">
-        <v>34</v>
-      </c>
-      <c r="C85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="E85">
+      <c r="D86" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86">
         <v>4445</v>
       </c>
-      <c r="F85">
+      <c r="F86">
         <v>611</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G86" s="2">
         <v>45286</v>
       </c>
-      <c r="H85">
-        <v>20</v>
-      </c>
-      <c r="I85">
+      <c r="H86">
+        <v>20</v>
+      </c>
+      <c r="I86">
         <v>33.979999999999997</v>
       </c>
-      <c r="J85">
+      <c r="J86">
         <v>15.42</v>
       </c>
-      <c r="K85">
+      <c r="K86">
         <v>453.79635079458512</v>
       </c>
-      <c r="L85">
+      <c r="L86">
         <v>0.50383333333333324</v>
       </c>
-      <c r="M85">
+      <c r="M86">
         <v>1.4819977784240319</v>
       </c>
-      <c r="N85">
+      <c r="N86">
         <v>516.94592</v>
       </c>
-      <c r="O85">
+      <c r="O86">
         <v>13.33713</v>
       </c>
-      <c r="P85">
+      <c r="P86">
         <v>0.67413284412384</v>
       </c>
-      <c r="Q85">
+      <c r="Q86">
         <v>2.8109981555599149E-2</v>
       </c>
-      <c r="R85">
+      <c r="R86">
         <v>4.9841233568780616</v>
       </c>
-      <c r="S85">
+      <c r="S86">
         <v>2.8074554228704678E-2</v>
       </c>
-      <c r="T85">
+      <c r="T86">
         <v>3.5390329947089638</v>
       </c>
-      <c r="U85">
+      <c r="U86">
         <v>4.6278841921501961</v>
       </c>
-      <c r="V85">
+      <c r="V86">
         <v>0</v>
       </c>
-      <c r="W85">
+      <c r="W86">
         <v>0</v>
       </c>
-      <c r="Y85">
+      <c r="Y86">
         <v>4445</v>
       </c>
-      <c r="Z85">
+      <c r="Z86">
         <v>557.89099999999996</v>
       </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>14</v>
-      </c>
-      <c r="B86" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" t="s">
-        <v>30</v>
-      </c>
-      <c r="D86" t="s">
-        <v>31</v>
-      </c>
-      <c r="E86">
-        <v>9738</v>
-      </c>
-      <c r="F86">
-        <v>664</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45288</v>
-      </c>
-      <c r="H86">
-        <v>20</v>
-      </c>
-      <c r="I86">
-        <v>18.21</v>
-      </c>
-      <c r="J86">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="K86">
-        <v>460.18671059857218</v>
-      </c>
-      <c r="L86">
-        <v>0.47983333333333328</v>
-      </c>
-      <c r="M86">
-        <v>1.3976456585853281</v>
-      </c>
-      <c r="N86">
-        <v>485.08228000000003</v>
-      </c>
-      <c r="O86">
-        <v>11.899430000000001</v>
-      </c>
-      <c r="P86">
-        <v>1.718324936833187</v>
-      </c>
-      <c r="Q86">
-        <v>0.13997819780744841</v>
-      </c>
-      <c r="R86">
-        <v>0.9082398463983633</v>
-      </c>
-      <c r="S86">
-        <v>5.6755173815428481E-2</v>
-      </c>
-      <c r="T86">
-        <v>3.263334026849352</v>
-      </c>
-      <c r="U86">
-        <v>1.2711599354276499</v>
-      </c>
-      <c r="V86">
-        <v>7.963006005094786E-2</v>
-      </c>
-      <c r="W86">
-        <v>0.77086571754539313</v>
-      </c>
-      <c r="Y86">
-        <v>9738</v>
-      </c>
-      <c r="Z86">
-        <v>294.20800000000003</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA86" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87">
+        <v>9738</v>
+      </c>
+      <c r="F87">
+        <v>664</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45288</v>
+      </c>
+      <c r="H87">
+        <v>20</v>
+      </c>
+      <c r="I87">
+        <v>18.21</v>
+      </c>
+      <c r="J87">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="K87">
+        <v>460.18671059857218</v>
+      </c>
+      <c r="L87">
+        <v>0.47983333333333328</v>
+      </c>
+      <c r="M87">
+        <v>1.3976456585853281</v>
+      </c>
+      <c r="N87">
+        <v>485.08228000000003</v>
+      </c>
+      <c r="O87">
+        <v>11.899430000000001</v>
+      </c>
+      <c r="P87">
+        <v>1.718324936833187</v>
+      </c>
+      <c r="Q87">
+        <v>0.13997819780744841</v>
+      </c>
+      <c r="R87">
+        <v>0.9082398463983633</v>
+      </c>
+      <c r="S87">
+        <v>5.6755173815428481E-2</v>
+      </c>
+      <c r="T87">
+        <v>3.263334026849352</v>
+      </c>
+      <c r="U87">
+        <v>1.2711599354276499</v>
+      </c>
+      <c r="V87">
+        <v>7.963006005094786E-2</v>
+      </c>
+      <c r="W87">
+        <v>0.77086571754539313</v>
+      </c>
+      <c r="Y87">
+        <v>9738</v>
+      </c>
+      <c r="Z87">
+        <v>294.20800000000003</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>14</v>
+      </c>
+      <c r="B88" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" t="s">
         <v>28</v>
       </c>
-      <c r="E87">
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88">
         <v>6976</v>
       </c>
-      <c r="F87">
+      <c r="F88">
         <v>674</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G88" s="2">
         <v>45287</v>
       </c>
-      <c r="H87">
-        <v>20</v>
-      </c>
-      <c r="I87">
+      <c r="H88">
+        <v>20</v>
+      </c>
+      <c r="I88">
         <v>46.52</v>
       </c>
-      <c r="J87">
+      <c r="J88">
         <v>19.96</v>
       </c>
-      <c r="K87">
+      <c r="K88">
         <v>429.06276870163367</v>
       </c>
-      <c r="L87">
+      <c r="L88">
         <v>0.5635</v>
       </c>
-      <c r="M87">
+      <c r="M88">
         <v>1.622584644821873</v>
       </c>
-      <c r="N87">
+      <c r="N88">
         <v>514.33613000000003</v>
       </c>
-      <c r="O87">
+      <c r="O88">
         <v>15.409560000000001</v>
       </c>
-      <c r="P87">
+      <c r="P88">
         <v>1.4455860548893169</v>
       </c>
-      <c r="Q87">
+      <c r="Q88">
         <v>0</v>
       </c>
-      <c r="R87">
+      <c r="R88">
         <v>3.2942730972211609</v>
       </c>
-      <c r="S87">
+      <c r="S88">
         <v>3.9484008141003883E-2</v>
       </c>
-      <c r="T87">
+      <c r="T88">
         <v>2.8356681780679498</v>
       </c>
-      <c r="U87">
+      <c r="U88">
         <v>3.2050281847549229</v>
       </c>
-      <c r="V87">
+      <c r="V88">
         <v>0.1835873522940365</v>
       </c>
-      <c r="W87">
+      <c r="W88">
         <v>0.79053143948538385</v>
       </c>
-      <c r="Y87">
+      <c r="Y88">
         <v>6976</v>
       </c>
-      <c r="Z87">
+      <c r="Z88">
         <v>656.96399999999994</v>
       </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>17</v>
-      </c>
-      <c r="B88" t="s">
-        <v>26</v>
-      </c>
-      <c r="C88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88">
-        <v>4932</v>
-      </c>
-      <c r="F88">
-        <v>882</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45290</v>
-      </c>
-      <c r="H88">
-        <v>20</v>
-      </c>
-      <c r="I88">
-        <v>44.48</v>
-      </c>
-      <c r="J88">
-        <v>18.829999999999998</v>
-      </c>
-      <c r="K88">
-        <v>423.33633093525179</v>
-      </c>
-      <c r="L88">
-        <v>0.5528333333333334</v>
-      </c>
-      <c r="M88">
-        <v>1.6294813590225219</v>
-      </c>
-      <c r="N88">
-        <v>484.54681000000011</v>
-      </c>
-      <c r="O88">
-        <v>12.853899999999999</v>
-      </c>
-      <c r="P88">
-        <v>0.62996643536925445</v>
-      </c>
-      <c r="Q88">
-        <v>5.3538279092846972</v>
-      </c>
-      <c r="R88">
-        <v>1.6711532051911699</v>
-      </c>
-      <c r="S88">
-        <v>4.5936219968964673E-2</v>
-      </c>
-      <c r="T88">
-        <v>8.5758837687889216</v>
-      </c>
-      <c r="U88">
-        <v>2.8033842021254491</v>
-      </c>
-      <c r="V88">
-        <v>7.0902549584492075E-2</v>
-      </c>
-      <c r="W88">
-        <v>0.94084539623400698</v>
-      </c>
-      <c r="Y88">
-        <v>4932</v>
-      </c>
-      <c r="Z88">
-        <v>696.71500000000003</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA88" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E89">
-        <v>7645</v>
+        <v>4932</v>
       </c>
       <c r="F89">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="G89" s="2">
         <v>45290</v>
@@ -7344,140 +7415,152 @@
         <v>20</v>
       </c>
       <c r="I89">
-        <v>52.58</v>
+        <v>44.48</v>
       </c>
       <c r="J89">
-        <v>23.72</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="K89">
-        <v>451.12209965766448</v>
+        <v>423.33633093525179</v>
       </c>
       <c r="L89">
-        <v>0.58350000000000002</v>
+        <v>0.5528333333333334</v>
       </c>
       <c r="M89">
-        <v>1.6825330067198201</v>
+        <v>1.6294813590225219</v>
       </c>
       <c r="N89">
-        <v>501.49704000000003</v>
+        <v>484.54681000000011</v>
       </c>
       <c r="O89">
-        <v>10.420120000000001</v>
+        <v>12.853899999999999</v>
       </c>
       <c r="P89">
-        <v>0.61258978053325874</v>
+        <v>0.62996643536925445</v>
       </c>
       <c r="Q89">
-        <v>6.4322207258186437E-2</v>
+        <v>5.3538279092846972</v>
       </c>
       <c r="R89">
-        <v>10.768010860691399</v>
+        <v>1.6711532051911699</v>
       </c>
       <c r="S89">
-        <v>2.9267627783012558E-2</v>
+        <v>4.5936219968964673E-2</v>
       </c>
       <c r="T89">
-        <v>3.5183066482733909</v>
+        <v>8.5758837687889216</v>
       </c>
       <c r="U89">
-        <v>3.7423397421012128</v>
+        <v>2.8033842021254491</v>
       </c>
       <c r="V89">
-        <v>8.1218154323550243E-2</v>
+        <v>7.0902549584492075E-2</v>
       </c>
       <c r="W89">
-        <v>0.60015109924284338</v>
+        <v>0.94084539623400698</v>
       </c>
       <c r="Y89">
-        <v>7645</v>
+        <v>4932</v>
       </c>
       <c r="Z89">
-        <v>765.00800000000004</v>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+        <v>696.71500000000003</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="E90">
+        <v>7645</v>
       </c>
       <c r="F90">
-        <v>4933</v>
+        <v>889</v>
       </c>
       <c r="G90" s="2">
-        <v>45294</v>
+        <v>45290</v>
       </c>
       <c r="H90">
         <v>20</v>
       </c>
       <c r="I90">
-        <v>17.09</v>
+        <v>52.58</v>
       </c>
       <c r="J90">
-        <v>8.77</v>
+        <v>23.72</v>
       </c>
       <c r="K90">
-        <v>513.16559391456997</v>
+        <v>451.12209965766448</v>
       </c>
       <c r="L90">
-        <v>0.46266666666666662</v>
+        <v>0.58350000000000002</v>
       </c>
       <c r="M90">
-        <v>1.5241738383433849</v>
+        <v>1.6825330067198201</v>
       </c>
       <c r="N90">
-        <v>498.50623999999999</v>
+        <v>501.49704000000003</v>
       </c>
       <c r="O90">
-        <v>10.546279999999999</v>
+        <v>10.420120000000001</v>
       </c>
       <c r="P90">
-        <v>0.42316206951753421</v>
+        <v>0.61258978053325874</v>
       </c>
       <c r="Q90">
-        <v>7.7413465076342294E-2</v>
+        <v>6.4322207258186437E-2</v>
       </c>
       <c r="R90">
-        <v>0.8864310941421033</v>
+        <v>10.768010860691399</v>
       </c>
       <c r="S90">
-        <v>4.7952576796205883E-2</v>
+        <v>2.9267627783012558E-2</v>
       </c>
       <c r="T90">
-        <v>3.457335577835881</v>
+        <v>3.5183066482733909</v>
       </c>
       <c r="U90">
-        <v>0.66432459277088485</v>
+        <v>3.7423397421012128</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>8.1218154323550243E-2</v>
       </c>
       <c r="W90">
-        <v>0.46010346073571751</v>
+        <v>0.60015109924284338</v>
+      </c>
+      <c r="Y90">
+        <v>7645</v>
       </c>
       <c r="Z90">
-        <v>282.59800000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+        <v>765.00800000000004</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E91">
         <v>5880</v>
@@ -7542,19 +7625,22 @@
       <c r="Z91">
         <v>403.00099999999998</v>
       </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA91" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E92">
         <v>4940</v>
@@ -7619,19 +7705,22 @@
       <c r="Z92">
         <v>554.20000000000005</v>
       </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA92" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E93">
         <v>4952</v>
@@ -7696,19 +7785,22 @@
       <c r="Z93">
         <v>417.774</v>
       </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA93" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E94">
         <v>4955</v>
@@ -7772,6 +7864,9 @@
       </c>
       <c r="Z94">
         <v>325.12799999999999</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Results_isofys/SFtraits_complete.xlsx
+++ b/Results_isofys/SFtraits_complete.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\SLA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\NUMEX_preliminar\Results_isofys\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="51">
-  <si>
-    <t>Plot_x</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="50">
   <si>
     <t>treat</t>
   </si>
@@ -179,7 +176,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -235,7 +232,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,85 +540,85 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -629,13 +626,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
       </c>
       <c r="F2">
         <v>69</v>
@@ -692,7 +689,7 @@
         <v>0.93375439562890372</v>
       </c>
       <c r="X2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2">
         <v>69</v>
@@ -706,13 +703,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
       </c>
       <c r="F3">
         <v>88</v>
@@ -769,7 +766,7 @@
         <v>0.64353137799262627</v>
       </c>
       <c r="X3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y3">
         <v>88</v>
@@ -783,13 +780,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
         <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
       </c>
       <c r="E4">
         <v>4966</v>
@@ -849,7 +846,7 @@
         <v>0.67216469219590569</v>
       </c>
       <c r="X4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y4">
         <v>90</v>
@@ -863,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
       </c>
       <c r="F5">
         <v>92</v>
@@ -926,7 +923,7 @@
         <v>0.54945171314582775</v>
       </c>
       <c r="X5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y5">
         <v>92</v>
@@ -940,13 +937,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -1003,7 +1000,7 @@
         <v>0.5953654546153796</v>
       </c>
       <c r="X6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6">
         <v>96</v>
@@ -1017,13 +1014,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
       </c>
       <c r="F7">
         <v>101</v>
@@ -1080,7 +1077,7 @@
         <v>0.52146683887209699</v>
       </c>
       <c r="X7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y7">
         <v>101</v>
@@ -1094,13 +1091,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
       <c r="F8">
         <v>9091</v>
@@ -1157,7 +1154,7 @@
         <v>0.30996191628373221</v>
       </c>
       <c r="X8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y8">
         <v>9091</v>
@@ -1171,13 +1168,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="F9">
         <v>9096</v>
@@ -1234,7 +1231,7 @@
         <v>0.50296884701541678</v>
       </c>
       <c r="X9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y9">
         <v>9096</v>
@@ -1248,13 +1245,13 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
         <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
       </c>
       <c r="F10">
         <v>254</v>
@@ -1311,7 +1308,7 @@
         <v>0.67448670723073889</v>
       </c>
       <c r="X10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y10">
         <v>254</v>
@@ -1325,13 +1322,13 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
       </c>
       <c r="F11">
         <v>267</v>
@@ -1388,7 +1385,7 @@
         <v>0.66634530256369617</v>
       </c>
       <c r="X11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y11">
         <v>267</v>
@@ -1402,13 +1399,13 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
         <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
       </c>
       <c r="F12">
         <v>141</v>
@@ -1465,7 +1462,7 @@
         <v>0.67888952384523749</v>
       </c>
       <c r="X12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y12">
         <v>141</v>
@@ -1479,13 +1476,13 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
         <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
       </c>
       <c r="F13">
         <v>143</v>
@@ -1542,7 +1539,7 @@
         <v>1.3602653623084251</v>
       </c>
       <c r="X13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y13">
         <v>143</v>
@@ -1556,13 +1553,13 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
         <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
       </c>
       <c r="F14">
         <v>155</v>
@@ -1619,7 +1616,7 @@
         <v>0.8671868366505725</v>
       </c>
       <c r="X14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y14">
         <v>155</v>
@@ -1633,13 +1630,13 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
         <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
       </c>
       <c r="F15">
         <v>172</v>
@@ -1696,7 +1693,7 @@
         <v>0.85954961186370971</v>
       </c>
       <c r="X15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y15">
         <v>172</v>
@@ -1710,13 +1707,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
         <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
       </c>
       <c r="F16">
         <v>188</v>
@@ -1773,7 +1770,7 @@
         <v>0.58545855970023564</v>
       </c>
       <c r="X16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y16">
         <v>188</v>
@@ -1787,13 +1784,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
         <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
       </c>
       <c r="F17">
         <v>191</v>
@@ -1850,7 +1847,7 @@
         <v>0.67055111744776807</v>
       </c>
       <c r="X17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y17">
         <v>191</v>
@@ -1864,13 +1861,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
         <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
       </c>
       <c r="F18">
         <v>200</v>
@@ -1927,7 +1924,7 @@
         <v>0.71175443978373909</v>
       </c>
       <c r="X18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y18">
         <v>200</v>
@@ -1941,13 +1938,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
         <v>31</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
       </c>
       <c r="F19">
         <v>205</v>
@@ -2004,7 +2001,7 @@
         <v>0.69790416786521037</v>
       </c>
       <c r="X19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y19">
         <v>205</v>
@@ -2018,13 +2015,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
         <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
       </c>
       <c r="F20">
         <v>209</v>
@@ -2081,7 +2078,7 @@
         <v>1.4227986302889579</v>
       </c>
       <c r="X20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y20">
         <v>209</v>
@@ -2095,13 +2092,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
         <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>29</v>
       </c>
       <c r="F21">
         <v>213</v>
@@ -2158,7 +2155,7 @@
         <v>0.63824183053382444</v>
       </c>
       <c r="X21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y21">
         <v>213</v>
@@ -2172,13 +2169,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
         <v>28</v>
-      </c>
-      <c r="D22" t="s">
-        <v>29</v>
       </c>
       <c r="F22">
         <v>219</v>
@@ -2235,7 +2232,7 @@
         <v>0.70762505809660969</v>
       </c>
       <c r="X22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y22">
         <v>219</v>
@@ -2249,13 +2246,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
         <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>29</v>
       </c>
       <c r="F23">
         <v>286</v>
@@ -2312,7 +2309,7 @@
         <v>0.65198182136378591</v>
       </c>
       <c r="X23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y23">
         <v>286</v>
@@ -2326,13 +2323,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
         <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>29</v>
       </c>
       <c r="F24">
         <v>290</v>
@@ -2389,7 +2386,7 @@
         <v>1.152817493965886</v>
       </c>
       <c r="X24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y24">
         <v>290</v>
@@ -2403,13 +2400,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
         <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>29</v>
       </c>
       <c r="F25">
         <v>310</v>
@@ -2466,7 +2463,7 @@
         <v>0.82568518152160986</v>
       </c>
       <c r="X25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y25">
         <v>310</v>
@@ -2480,13 +2477,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
       </c>
       <c r="F26">
         <v>6021</v>
@@ -2543,7 +2540,7 @@
         <v>0.65361373069631201</v>
       </c>
       <c r="X26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y26">
         <v>6021</v>
@@ -2557,13 +2554,13 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
       </c>
       <c r="F27">
         <v>333</v>
@@ -2620,7 +2617,7 @@
         <v>0.67284165998378676</v>
       </c>
       <c r="X27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y27">
         <v>333</v>
@@ -2634,13 +2631,13 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
         <v>27</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>28</v>
-      </c>
-      <c r="D28" t="s">
-        <v>29</v>
       </c>
       <c r="F28">
         <v>335</v>
@@ -2697,7 +2694,7 @@
         <v>0.60745506559882334</v>
       </c>
       <c r="X28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y28">
         <v>335</v>
@@ -2711,13 +2708,13 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
-      </c>
-      <c r="D29" t="s">
-        <v>32</v>
       </c>
       <c r="F29">
         <v>341</v>
@@ -2774,7 +2771,7 @@
         <v>0.64538435640185099</v>
       </c>
       <c r="X29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y29">
         <v>341</v>
@@ -2788,13 +2785,13 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
         <v>27</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>28</v>
-      </c>
-      <c r="D30" t="s">
-        <v>29</v>
       </c>
       <c r="F30">
         <v>356</v>
@@ -2851,7 +2848,7 @@
         <v>0.62731443320284119</v>
       </c>
       <c r="X30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y30">
         <v>356</v>
@@ -2865,13 +2862,13 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
         <v>27</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>28</v>
-      </c>
-      <c r="D31" t="s">
-        <v>29</v>
       </c>
       <c r="F31">
         <v>6994</v>
@@ -2928,7 +2925,7 @@
         <v>0.73289884442324349</v>
       </c>
       <c r="X31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y31">
         <v>6994</v>
@@ -2942,13 +2939,13 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
       </c>
       <c r="F32">
         <v>7994</v>
@@ -3005,7 +3002,7 @@
         <v>0.60720166686426202</v>
       </c>
       <c r="X32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y32">
         <v>7994</v>
@@ -3019,13 +3016,13 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
       </c>
       <c r="F33">
         <v>378</v>
@@ -3082,7 +3079,7 @@
         <v>0.54955023184554519</v>
       </c>
       <c r="X33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y33">
         <v>378</v>
@@ -3096,13 +3093,13 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
         <v>28</v>
-      </c>
-      <c r="D34" t="s">
-        <v>29</v>
       </c>
       <c r="F34">
         <v>389</v>
@@ -3159,7 +3156,7 @@
         <v>0.65267718541780073</v>
       </c>
       <c r="X34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y34">
         <v>389</v>
@@ -3173,13 +3170,13 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
         <v>28</v>
-      </c>
-      <c r="D35" t="s">
-        <v>29</v>
       </c>
       <c r="F35">
         <v>410</v>
@@ -3236,7 +3233,7 @@
         <v>0.9163775544555931</v>
       </c>
       <c r="X35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y35">
         <v>410</v>
@@ -3250,13 +3247,13 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
         <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
       </c>
       <c r="F36">
         <v>9080</v>
@@ -3313,7 +3310,7 @@
         <v>0.39055729029571518</v>
       </c>
       <c r="X36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y36">
         <v>9080</v>
@@ -3327,13 +3324,13 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
         <v>28</v>
-      </c>
-      <c r="D37" t="s">
-        <v>29</v>
       </c>
       <c r="F37">
         <v>569</v>
@@ -3390,7 +3387,7 @@
         <v>0.6895798104979235</v>
       </c>
       <c r="X37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y37">
         <v>569</v>
@@ -3404,13 +3401,13 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
         <v>28</v>
-      </c>
-      <c r="D38" t="s">
-        <v>29</v>
       </c>
       <c r="F38">
         <v>575</v>
@@ -3467,7 +3464,7 @@
         <v>0.57025958917460684</v>
       </c>
       <c r="X38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y38">
         <v>575</v>
@@ -3481,13 +3478,13 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
         <v>31</v>
-      </c>
-      <c r="D39" t="s">
-        <v>32</v>
       </c>
       <c r="F39">
         <v>580</v>
@@ -3544,7 +3541,7 @@
         <v>1.392603334482716</v>
       </c>
       <c r="X39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y39">
         <v>580</v>
@@ -3558,13 +3555,13 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
         <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>29</v>
       </c>
       <c r="F40">
         <v>587</v>
@@ -3621,7 +3618,7 @@
         <v>0.65272487799156209</v>
       </c>
       <c r="X40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y40">
         <v>587</v>
@@ -3635,13 +3632,13 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
         <v>28</v>
-      </c>
-      <c r="D41" t="s">
-        <v>29</v>
       </c>
       <c r="F41">
         <v>596</v>
@@ -3698,7 +3695,7 @@
         <v>0.57119399416423045</v>
       </c>
       <c r="X41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y41">
         <v>596</v>
@@ -3712,13 +3709,13 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
         <v>31</v>
-      </c>
-      <c r="D42" t="s">
-        <v>32</v>
       </c>
       <c r="F42">
         <v>915</v>
@@ -3775,7 +3772,7 @@
         <v>0.65619644928845844</v>
       </c>
       <c r="X42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y42">
         <v>915</v>
@@ -3789,13 +3786,13 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" t="s">
         <v>31</v>
-      </c>
-      <c r="D43" t="s">
-        <v>32</v>
       </c>
       <c r="F43">
         <v>708</v>
@@ -3852,7 +3849,7 @@
         <v>1.0749599826320391</v>
       </c>
       <c r="X43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y43">
         <v>708</v>
@@ -3866,13 +3863,13 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
         <v>31</v>
-      </c>
-      <c r="D44" t="s">
-        <v>32</v>
       </c>
       <c r="F44">
         <v>721</v>
@@ -3929,7 +3926,7 @@
         <v>0.86234695562764752</v>
       </c>
       <c r="X44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y44">
         <v>721</v>
@@ -3943,13 +3940,13 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
         <v>31</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
       </c>
       <c r="F45">
         <v>729</v>
@@ -4006,7 +4003,7 @@
         <v>0.82236954012352836</v>
       </c>
       <c r="X45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y45">
         <v>729</v>
@@ -4020,13 +4017,13 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" t="s">
         <v>31</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
       </c>
       <c r="F46">
         <v>627</v>
@@ -4083,7 +4080,7 @@
         <v>0.58739035651902571</v>
       </c>
       <c r="X46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y46">
         <v>627</v>
@@ -4097,13 +4094,13 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
         <v>28</v>
-      </c>
-      <c r="D47" t="s">
-        <v>29</v>
       </c>
       <c r="F47">
         <v>631</v>
@@ -4160,7 +4157,7 @@
         <v>0.51926604097941564</v>
       </c>
       <c r="X47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y47">
         <v>631</v>
@@ -4174,13 +4171,13 @@
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
         <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>29</v>
       </c>
       <c r="F48">
         <v>642</v>
@@ -4237,7 +4234,7 @@
         <v>0.75479895908546057</v>
       </c>
       <c r="X48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y48">
         <v>642</v>
@@ -4251,13 +4248,13 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
         <v>31</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
       </c>
       <c r="F49">
         <v>9742</v>
@@ -4314,7 +4311,7 @@
         <v>0.74099114632419627</v>
       </c>
       <c r="X49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y49">
         <v>9742</v>
@@ -4328,13 +4325,13 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
         <v>31</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
       </c>
       <c r="F50">
         <v>659</v>
@@ -4391,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="X50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y50">
         <v>659</v>
@@ -4405,13 +4402,13 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" t="s">
         <v>31</v>
-      </c>
-      <c r="D51" t="s">
-        <v>32</v>
       </c>
       <c r="F51">
         <v>666</v>
@@ -4468,7 +4465,7 @@
         <v>0.75540141003846228</v>
       </c>
       <c r="X51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y51">
         <v>666</v>
@@ -4482,13 +4479,13 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" t="s">
         <v>31</v>
-      </c>
-      <c r="D52" t="s">
-        <v>32</v>
       </c>
       <c r="F52">
         <v>685</v>
@@ -4545,7 +4542,7 @@
         <v>0.77794552241096226</v>
       </c>
       <c r="X52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y52">
         <v>685</v>
@@ -4559,13 +4556,13 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" t="s">
         <v>31</v>
-      </c>
-      <c r="D53" t="s">
-        <v>32</v>
       </c>
       <c r="F53">
         <v>693</v>
@@ -4622,7 +4619,7 @@
         <v>0.73874634149960039</v>
       </c>
       <c r="X53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y53">
         <v>693</v>
@@ -4636,13 +4633,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="s">
         <v>31</v>
-      </c>
-      <c r="D54" t="s">
-        <v>32</v>
       </c>
       <c r="F54">
         <v>740</v>
@@ -4699,7 +4696,7 @@
         <v>0.51968405938420781</v>
       </c>
       <c r="X54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y54">
         <v>740</v>
@@ -4713,13 +4710,13 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" t="s">
         <v>31</v>
-      </c>
-      <c r="D55" t="s">
-        <v>32</v>
       </c>
       <c r="F55">
         <v>746</v>
@@ -4776,7 +4773,7 @@
         <v>0.50188962336462528</v>
       </c>
       <c r="X55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y55">
         <v>746</v>
@@ -4790,13 +4787,13 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s">
         <v>28</v>
-      </c>
-      <c r="D56" t="s">
-        <v>29</v>
       </c>
       <c r="F56">
         <v>755</v>
@@ -4853,7 +4850,7 @@
         <v>0.66859423229833526</v>
       </c>
       <c r="X56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y56">
         <v>755</v>
@@ -4867,13 +4864,13 @@
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
         <v>28</v>
-      </c>
-      <c r="D57" t="s">
-        <v>29</v>
       </c>
       <c r="F57">
         <v>763</v>
@@ -4930,7 +4927,7 @@
         <v>0.5161964358633585</v>
       </c>
       <c r="X57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y57">
         <v>763</v>
@@ -4944,13 +4941,13 @@
         <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" t="s">
         <v>31</v>
-      </c>
-      <c r="D58" t="s">
-        <v>32</v>
       </c>
       <c r="F58">
         <v>764</v>
@@ -5007,7 +5004,7 @@
         <v>0.63599797304952554</v>
       </c>
       <c r="X58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y58">
         <v>764</v>
@@ -5021,13 +5018,13 @@
         <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
+        <v>30</v>
+      </c>
+      <c r="D59" t="s">
         <v>31</v>
-      </c>
-      <c r="D59" t="s">
-        <v>32</v>
       </c>
       <c r="F59">
         <v>768</v>
@@ -5084,7 +5081,7 @@
         <v>0.72542985723080833</v>
       </c>
       <c r="X59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y59">
         <v>768</v>
@@ -5098,13 +5095,13 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
         <v>27</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>28</v>
-      </c>
-      <c r="D60" t="s">
-        <v>29</v>
       </c>
       <c r="F60">
         <v>881</v>
@@ -5161,7 +5158,7 @@
         <v>0.81765344957248842</v>
       </c>
       <c r="X60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y60">
         <v>881</v>
@@ -5175,13 +5172,13 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" t="s">
         <v>31</v>
-      </c>
-      <c r="D61" t="s">
-        <v>32</v>
       </c>
       <c r="F61">
         <v>902</v>
@@ -5238,7 +5235,7 @@
         <v>2.2789143560634089</v>
       </c>
       <c r="X61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y61">
         <v>902</v>
@@ -5252,13 +5249,13 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" t="s">
         <v>31</v>
-      </c>
-      <c r="D62" t="s">
-        <v>32</v>
       </c>
       <c r="F62">
         <v>4933</v>
@@ -5315,7 +5312,7 @@
         <v>0.46010346073571751</v>
       </c>
       <c r="X62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y62">
         <v>4933</v>
@@ -5329,13 +5326,13 @@
         <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" t="s">
         <v>31</v>
-      </c>
-      <c r="D63" t="s">
-        <v>32</v>
       </c>
       <c r="F63">
         <v>8954</v>
@@ -5392,7 +5389,7 @@
         <v>0.47255541116350408</v>
       </c>
       <c r="X63" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y63">
         <v>8954</v>
@@ -5406,13 +5403,13 @@
         <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" t="s">
         <v>31</v>
-      </c>
-      <c r="D64" t="s">
-        <v>32</v>
       </c>
       <c r="F64">
         <v>816</v>
@@ -5469,7 +5466,7 @@
         <v>4.3087054495614536</v>
       </c>
       <c r="X64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y64">
         <v>816</v>
@@ -5483,13 +5480,13 @@
         <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" t="s">
         <v>31</v>
-      </c>
-      <c r="D65" t="s">
-        <v>32</v>
       </c>
       <c r="F65">
         <v>7578</v>
@@ -5546,7 +5543,7 @@
         <v>0.27510476713466719</v>
       </c>
       <c r="X65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y65">
         <v>7578</v>
@@ -5560,13 +5557,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" t="s">
         <v>31</v>
-      </c>
-      <c r="D66" t="s">
-        <v>32</v>
       </c>
       <c r="F66">
         <v>795</v>
@@ -5623,7 +5620,7 @@
         <v>0.88961263793631462</v>
       </c>
       <c r="X66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y66">
         <v>795</v>
@@ -5637,13 +5634,13 @@
         <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" t="s">
         <v>31</v>
-      </c>
-      <c r="D67" t="s">
-        <v>32</v>
       </c>
       <c r="F67">
         <v>798</v>
@@ -5700,7 +5697,7 @@
         <v>0.92661537699513896</v>
       </c>
       <c r="X67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y67">
         <v>798</v>
@@ -5714,13 +5711,13 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" t="s">
         <v>31</v>
-      </c>
-      <c r="D68" t="s">
-        <v>32</v>
       </c>
       <c r="E68">
         <v>5812</v>
@@ -5786,7 +5783,7 @@
         <v>367.36099999999999</v>
       </c>
       <c r="AA68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
@@ -5794,13 +5791,13 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" t="s">
         <v>31</v>
-      </c>
-      <c r="D69" t="s">
-        <v>32</v>
       </c>
       <c r="E69">
         <v>8386</v>
@@ -5866,7 +5863,7 @@
         <v>270.44099999999997</v>
       </c>
       <c r="AA69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
@@ -5874,13 +5871,13 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="s">
         <v>28</v>
-      </c>
-      <c r="D70" t="s">
-        <v>29</v>
       </c>
       <c r="E70">
         <v>7922</v>
@@ -5946,7 +5943,7 @@
         <v>633.245</v>
       </c>
       <c r="AA70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
@@ -5954,13 +5951,13 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" t="s">
         <v>31</v>
-      </c>
-      <c r="D71" t="s">
-        <v>32</v>
       </c>
       <c r="E71">
         <v>9084</v>
@@ -6026,7 +6023,7 @@
         <v>344.25900000000001</v>
       </c>
       <c r="AA71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
@@ -6034,13 +6031,13 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
         <v>28</v>
-      </c>
-      <c r="D72" t="s">
-        <v>29</v>
       </c>
       <c r="E72">
         <v>7924</v>
@@ -6106,7 +6103,7 @@
         <v>876.08899999999994</v>
       </c>
       <c r="AA72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.25">
@@ -6114,13 +6111,13 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" t="s">
         <v>31</v>
-      </c>
-      <c r="D73" t="s">
-        <v>32</v>
       </c>
       <c r="E73">
         <v>8384</v>
@@ -6186,7 +6183,7 @@
         <v>306.63299999999998</v>
       </c>
       <c r="AA73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
@@ -6194,13 +6191,13 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
         <v>28</v>
-      </c>
-      <c r="D74" t="s">
-        <v>29</v>
       </c>
       <c r="E74">
         <v>8396</v>
@@ -6266,7 +6263,7 @@
         <v>597.89800000000002</v>
       </c>
       <c r="AA74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
@@ -6274,13 +6271,13 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" t="s">
         <v>31</v>
-      </c>
-      <c r="D75" t="s">
-        <v>32</v>
       </c>
       <c r="E75">
         <v>9090</v>
@@ -6346,7 +6343,7 @@
         <v>618.99599999999998</v>
       </c>
       <c r="AA75" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
@@ -6354,13 +6351,13 @@
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" t="s">
         <v>31</v>
-      </c>
-      <c r="D76" t="s">
-        <v>32</v>
       </c>
       <c r="E76">
         <v>5807</v>
@@ -6426,7 +6423,7 @@
         <v>559.16999999999996</v>
       </c>
       <c r="AA76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
@@ -6434,13 +6431,13 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" t="s">
         <v>31</v>
-      </c>
-      <c r="D77" t="s">
-        <v>32</v>
       </c>
       <c r="E77">
         <v>8381</v>
@@ -6506,7 +6503,7 @@
         <v>358.34199999999998</v>
       </c>
       <c r="AA77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
@@ -6514,13 +6511,13 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C78" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" t="s">
         <v>31</v>
-      </c>
-      <c r="D78" t="s">
-        <v>32</v>
       </c>
       <c r="E78">
         <v>4905</v>
@@ -6586,7 +6583,7 @@
         <v>380.87099999999998</v>
       </c>
       <c r="AA78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
@@ -6594,13 +6591,13 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C79" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" t="s">
         <v>31</v>
-      </c>
-      <c r="D79" t="s">
-        <v>32</v>
       </c>
       <c r="E79">
         <v>6992</v>
@@ -6666,7 +6663,7 @@
         <v>250.54300000000001</v>
       </c>
       <c r="AA79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.25">
@@ -6674,13 +6671,13 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s">
         <v>28</v>
-      </c>
-      <c r="D80" t="s">
-        <v>29</v>
       </c>
       <c r="E80">
         <v>7237</v>
@@ -6746,7 +6743,7 @@
         <v>576.95299999999997</v>
       </c>
       <c r="AA80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.25">
@@ -6754,13 +6751,13 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" t="s">
         <v>28</v>
-      </c>
-      <c r="D81" t="s">
-        <v>29</v>
       </c>
       <c r="E81">
         <v>8361</v>
@@ -6826,7 +6823,7 @@
         <v>431.43200000000002</v>
       </c>
       <c r="AA81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.25">
@@ -6834,13 +6831,13 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" t="s">
         <v>28</v>
-      </c>
-      <c r="D82" t="s">
-        <v>29</v>
       </c>
       <c r="E82">
         <v>4469</v>
@@ -6906,7 +6903,7 @@
         <v>670.822</v>
       </c>
       <c r="AA82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.25">
@@ -6914,13 +6911,13 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" t="s">
         <v>31</v>
-      </c>
-      <c r="D83" t="s">
-        <v>32</v>
       </c>
       <c r="E83">
         <v>4898</v>
@@ -6986,7 +6983,7 @@
         <v>417.17200000000003</v>
       </c>
       <c r="AA83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.25">
@@ -6994,13 +6991,13 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
         <v>27</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>28</v>
-      </c>
-      <c r="D84" t="s">
-        <v>29</v>
       </c>
       <c r="E84">
         <v>4894</v>
@@ -7066,7 +7063,7 @@
         <v>427.81799999999998</v>
       </c>
       <c r="AA84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
@@ -7074,13 +7071,13 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
         <v>27</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>28</v>
-      </c>
-      <c r="D85" t="s">
-        <v>29</v>
       </c>
       <c r="E85">
         <v>7594</v>
@@ -7146,7 +7143,7 @@
         <v>482.79700000000003</v>
       </c>
       <c r="AA85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.25">
@@ -7154,13 +7151,13 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s">
         <v>28</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
       </c>
       <c r="E86">
         <v>4445</v>
@@ -7226,7 +7223,7 @@
         <v>557.89099999999996</v>
       </c>
       <c r="AA86" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.25">
@@ -7234,13 +7231,13 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C87" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" t="s">
         <v>31</v>
-      </c>
-      <c r="D87" t="s">
-        <v>32</v>
       </c>
       <c r="E87">
         <v>9738</v>
@@ -7306,7 +7303,7 @@
         <v>294.20800000000003</v>
       </c>
       <c r="AA87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.25">
@@ -7314,13 +7311,13 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C88" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s">
         <v>28</v>
-      </c>
-      <c r="D88" t="s">
-        <v>29</v>
       </c>
       <c r="E88">
         <v>6976</v>
@@ -7386,7 +7383,7 @@
         <v>656.96399999999994</v>
       </c>
       <c r="AA88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.25">
@@ -7394,13 +7391,13 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
         <v>27</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>28</v>
-      </c>
-      <c r="D89" t="s">
-        <v>29</v>
       </c>
       <c r="E89">
         <v>4932</v>
@@ -7466,7 +7463,7 @@
         <v>696.71500000000003</v>
       </c>
       <c r="AA89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.25">
@@ -7474,13 +7471,13 @@
         <v>17</v>
       </c>
       <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
         <v>27</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>28</v>
-      </c>
-      <c r="D90" t="s">
-        <v>29</v>
       </c>
       <c r="E90">
         <v>7645</v>
@@ -7546,7 +7543,7 @@
         <v>765.00800000000004</v>
       </c>
       <c r="AA90" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.25">
@@ -7554,13 +7551,13 @@
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C91" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91" t="s">
         <v>31</v>
-      </c>
-      <c r="D91" t="s">
-        <v>32</v>
       </c>
       <c r="E91">
         <v>5880</v>
@@ -7626,7 +7623,7 @@
         <v>403.00099999999998</v>
       </c>
       <c r="AA91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
@@ -7634,13 +7631,13 @@
         <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s">
         <v>28</v>
-      </c>
-      <c r="D92" t="s">
-        <v>29</v>
       </c>
       <c r="E92">
         <v>4940</v>
@@ -7706,7 +7703,7 @@
         <v>554.20000000000005</v>
       </c>
       <c r="AA92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.25">
@@ -7714,13 +7711,13 @@
         <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" t="s">
         <v>31</v>
-      </c>
-      <c r="D93" t="s">
-        <v>32</v>
       </c>
       <c r="E93">
         <v>4952</v>
@@ -7786,7 +7783,7 @@
         <v>417.774</v>
       </c>
       <c r="AA93" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
@@ -7794,13 +7791,13 @@
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C94" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" t="s">
         <v>28</v>
-      </c>
-      <c r="D94" t="s">
-        <v>29</v>
       </c>
       <c r="E94">
         <v>4955</v>
@@ -7866,7 +7863,7 @@
         <v>325.12799999999999</v>
       </c>
       <c r="AA94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
